--- a/01.Documentation/Control de versiones de Sistema.xlsx
+++ b/01.Documentation/Control de versiones de Sistema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Team Dropbox\JRODRIGUEZ\Repositorios\01.Rover\01.Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53854AA6-42C6-43AD-959E-A7034D0F5B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D3025C-5A47-484F-BB65-C28CF5F5FE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10637" yWindow="9154" windowWidth="22148" windowHeight="13200" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
+    <workbookView xWindow="-26850" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
   </bookViews>
   <sheets>
     <sheet name="ROVER" sheetId="1" r:id="rId1"/>
@@ -37,12 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
   <si>
     <t>Version</t>
-  </si>
-  <si>
-    <t>RCA y Cheyenne</t>
   </si>
   <si>
     <t>Cambios</t>
@@ -119,13 +116,25 @@
   </si>
   <si>
     <t>Modificacion Protocolo de arranque</t>
+  </si>
+  <si>
+    <t>Cheyenne</t>
+  </si>
+  <si>
+    <t>RCA</t>
+  </si>
+  <si>
+    <t>PMU</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +176,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -248,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -272,6 +287,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -281,14 +302,49 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -459,8 +515,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{90806AD9-57A0-44C6-AF8E-190F018DF894}" name="Tabla4" displayName="Tabla4" ref="A2:K12" totalsRowShown="0" headerRowDxfId="9">
-  <autoFilter ref="A2:K12" xr:uid="{90806AD9-57A0-44C6-AF8E-190F018DF894}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{90806AD9-57A0-44C6-AF8E-190F018DF894}" name="Tabla4" displayName="Tabla4" ref="A2:M12" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A2:M12" xr:uid="{90806AD9-57A0-44C6-AF8E-190F018DF894}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -472,28 +528,32 @@
     <filterColumn colId="8" hiddenButton="1"/>
     <filterColumn colId="9" hiddenButton="1"/>
     <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="11">
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{9FA54F9E-2B64-46C7-8724-4F53C0A8439C}" name="Version"/>
     <tableColumn id="2" xr3:uid="{3BE54A87-5E5F-4EA3-BDAB-A0C720984238}" name="Cambios"/>
-    <tableColumn id="3" xr3:uid="{AB20F20E-49A9-4665-BD7A-F644581AFA75}" name="RCA y Cheyenne" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{976DCCAB-C6EC-4C62-8AC5-08A36B372CCE}" name="Dan Kubin" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{D8284D0B-ADBD-41A0-A6F9-7641CE1B7BDC}" name="DCDC" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{46E385B5-AB98-4D3A-916E-D4AA04D7017C}" name="CPU" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{6881E89A-66E6-4690-9A39-537CA0759BA2}" name="CONNECTOR" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{333BA288-762B-4F9F-A286-6C24A87FF42E}" name="FLEX11" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{A160592F-145D-4517-BDD4-927375D826DF}" name="BOM_CONNECTOR" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{7927406B-7180-4F6C-8379-776F57D21C0A}" name="BOM_CPU" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{63BFBD1E-028C-45CC-A003-0A155CB27E7D}" name="BOM_DCDC" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{AB20F20E-49A9-4665-BD7A-F644581AFA75}" name="RCA" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{7196F99C-E490-4F1B-B33E-7EFD7CD01FDA}" name="Cheyenne" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{28E24DC9-EEC6-43C8-B3F3-C090F80BA90D}" name="PMU" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{976DCCAB-C6EC-4C62-8AC5-08A36B372CCE}" name="Dan Kubin" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{D8284D0B-ADBD-41A0-A6F9-7641CE1B7BDC}" name="DCDC" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{46E385B5-AB98-4D3A-916E-D4AA04D7017C}" name="CPU" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{6881E89A-66E6-4690-9A39-537CA0759BA2}" name="CONNECTOR" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{333BA288-762B-4F9F-A286-6C24A87FF42E}" name="FLEX11" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{A160592F-145D-4517-BDD4-927375D826DF}" name="BOM_CONNECTOR" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{7927406B-7180-4F6C-8379-776F57D21C0A}" name="BOM_CPU" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{63BFBD1E-028C-45CC-A003-0A155CB27E7D}" name="BOM_DCDC" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -531,7 +591,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -637,7 +697,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -779,7 +839,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -787,365 +847,432 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BF0786-E6C7-4307-9339-45491EF3032D}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3000</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+      <c r="E3" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3001</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3099</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9000</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3020</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="7">
-        <v>5</v>
-      </c>
-      <c r="F7" s="7">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G7" s="7">
+        <v>5</v>
+      </c>
+      <c r="H7" s="7">
+        <v>5</v>
+      </c>
+      <c r="I7" s="7">
         <v>2</v>
       </c>
-      <c r="H7" s="7">
+      <c r="J7" s="7">
         <v>1</v>
       </c>
-      <c r="I7" s="7">
-        <v>5</v>
-      </c>
-      <c r="J7" s="7">
+      <c r="K7" s="7">
+        <v>5</v>
+      </c>
+      <c r="L7" s="7">
         <v>9</v>
       </c>
-      <c r="K7" s="7">
+      <c r="M7" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3002</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="7">
-        <v>5</v>
-      </c>
-      <c r="F8" s="7">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="G8" s="7">
+        <v>5</v>
+      </c>
+      <c r="H8" s="7">
+        <v>5</v>
+      </c>
+      <c r="I8" s="7">
         <v>2</v>
       </c>
-      <c r="H8" s="7">
+      <c r="J8" s="7">
         <v>1</v>
       </c>
-      <c r="I8" s="7">
-        <v>5</v>
-      </c>
-      <c r="J8" s="7">
+      <c r="K8" s="7">
+        <v>5</v>
+      </c>
+      <c r="L8" s="7">
         <v>9</v>
       </c>
-      <c r="K8" s="7">
+      <c r="M8" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3030</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>22</v>
+      <c r="B9" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="7">
-        <v>5</v>
-      </c>
-      <c r="F9" s="7">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G9" s="7">
+        <v>5</v>
+      </c>
+      <c r="H9" s="7">
+        <v>5</v>
+      </c>
+      <c r="I9" s="7">
         <v>2</v>
       </c>
-      <c r="H9" s="7">
+      <c r="J9" s="7">
         <v>1</v>
       </c>
-      <c r="I9" s="7">
-        <v>5</v>
-      </c>
-      <c r="J9" s="7">
+      <c r="K9" s="7">
+        <v>5</v>
+      </c>
+      <c r="L9" s="7">
         <v>9</v>
       </c>
-      <c r="K9" s="7">
+      <c r="M9" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3003</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>22</v>
+      <c r="B10" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="7">
-        <v>5</v>
-      </c>
-      <c r="F10" s="7">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="G10" s="7">
+        <v>5</v>
+      </c>
+      <c r="H10" s="7">
+        <v>5</v>
+      </c>
+      <c r="I10" s="7">
         <v>2</v>
       </c>
-      <c r="H10" s="7">
+      <c r="J10" s="7">
         <v>1</v>
       </c>
-      <c r="I10" s="7">
-        <v>5</v>
-      </c>
-      <c r="J10" s="7">
+      <c r="K10" s="7">
+        <v>5</v>
+      </c>
+      <c r="L10" s="7">
         <v>9</v>
       </c>
-      <c r="K10" s="7">
+      <c r="M10" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3040</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="7">
-        <v>5</v>
-      </c>
-      <c r="F11" s="7">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G11" s="7">
+        <v>5</v>
+      </c>
+      <c r="H11" s="7">
+        <v>5</v>
+      </c>
+      <c r="I11" s="7">
         <v>2</v>
       </c>
-      <c r="H11" s="7">
+      <c r="J11" s="7">
         <v>1</v>
       </c>
-      <c r="I11" s="7">
-        <v>5</v>
-      </c>
-      <c r="J11" s="7">
+      <c r="K11" s="7">
+        <v>5</v>
+      </c>
+      <c r="L11" s="7">
         <v>9</v>
       </c>
-      <c r="K11" s="7">
+      <c r="M11" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3004</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="7">
-        <v>5</v>
-      </c>
-      <c r="F12" s="7">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="G12" s="7">
+        <v>5</v>
+      </c>
+      <c r="H12" s="7">
+        <v>5</v>
+      </c>
+      <c r="I12" s="7">
         <v>2</v>
       </c>
-      <c r="H12" s="7">
+      <c r="J12" s="7">
         <v>1</v>
       </c>
-      <c r="I12" s="7">
-        <v>5</v>
-      </c>
-      <c r="J12" s="7">
+      <c r="K12" s="7">
+        <v>5</v>
+      </c>
+      <c r="L12" s="7">
         <v>9</v>
       </c>
-      <c r="K12" s="7">
+      <c r="M12" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="25" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="C1:D1"/>
+  <mergeCells count="5">
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">

--- a/01.Documentation/Control de versiones de Sistema.xlsx
+++ b/01.Documentation/Control de versiones de Sistema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Team Dropbox\JRODRIGUEZ\Repositorios\01.Rover\01.Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D76E28-A89E-4822-8141-C3871DFBBD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341F3D1D-5E07-4025-9EB0-3BB9354F13DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
+    <workbookView xWindow="-18615" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
   </bookViews>
   <sheets>
     <sheet name="ROVER" sheetId="1" r:id="rId1"/>
@@ -458,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -470,25 +470,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -500,28 +485,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -529,9 +493,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -549,7 +510,40 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -869,74 +863,74 @@
   <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="6" customWidth="1"/>
-    <col min="4" max="6" width="12.140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="8" style="6" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="6" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="6" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.42578125" style="6"/>
+    <col min="3" max="3" width="17.5703125" style="5" customWidth="1"/>
+    <col min="4" max="6" width="12.140625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="8" style="5" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -945,73 +939,73 @@
     </row>
     <row r="7" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="10" t="s">
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="11" t="s">
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="12" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="15"/>
+      <c r="N9" s="24"/>
     </row>
     <row r="10" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1030,10 +1024,10 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="23"/>
+      <c r="N10" s="11"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1052,10 +1046,10 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="23"/>
+      <c r="N11" s="11"/>
     </row>
     <row r="12" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="16" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1074,10 +1068,10 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="23"/>
+      <c r="N12" s="11"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="16" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1116,19 +1110,19 @@
       <c r="M13" s="4">
         <v>10</v>
       </c>
-      <c r="N13" s="23"/>
+      <c r="N13" s="11"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -1158,10 +1152,10 @@
       <c r="M14" s="4">
         <v>10</v>
       </c>
-      <c r="N14" s="23"/>
+      <c r="N14" s="11"/>
     </row>
     <row r="15" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="16" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1200,10 +1194,10 @@
       <c r="M15" s="4">
         <v>10</v>
       </c>
-      <c r="N15" s="23"/>
+      <c r="N15" s="11"/>
     </row>
     <row r="16" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="16" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1242,10 +1236,10 @@
       <c r="M16" s="4">
         <v>10</v>
       </c>
-      <c r="N16" s="23"/>
+      <c r="N16" s="11"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="16" t="s">
         <v>36</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1260,7 +1254,7 @@
       <c r="E17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="4">
@@ -1284,19 +1278,19 @@
       <c r="M17" s="4">
         <v>10</v>
       </c>
-      <c r="N17" s="23"/>
+      <c r="N17" s="11"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="16" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E18" s="4" t="s">
@@ -1326,25 +1320,25 @@
       <c r="M18" s="4">
         <v>10</v>
       </c>
-      <c r="N18" s="23"/>
+      <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="16" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G19" s="4">
@@ -1368,25 +1362,27 @@
       <c r="M19" s="4">
         <v>10</v>
       </c>
-      <c r="N19" s="23"/>
+      <c r="N19" s="11">
+        <v>6</v>
+      </c>
     </row>
     <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="16" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="4">
@@ -1410,25 +1406,27 @@
       <c r="M20" s="4">
         <v>10</v>
       </c>
-      <c r="N20" s="23"/>
+      <c r="N20" s="11">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G21" s="4">
@@ -1452,1255 +1450,1257 @@
       <c r="M21" s="4">
         <v>10</v>
       </c>
-      <c r="N21" s="23"/>
+      <c r="N21" s="11">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
+      <c r="A22" s="16"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="23"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="11"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="23"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="11"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="23"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="11"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
+      <c r="A25" s="16"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="23"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
+      <c r="A26" s="16"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="23"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="11"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
+      <c r="A27" s="16"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="23"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="11"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="23"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="23"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="11"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
+      <c r="A30" s="16"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="23"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="11"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="23"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
+      <c r="A32" s="16"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="23"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="11"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
+      <c r="A33" s="16"/>
       <c r="B33" s="1"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="23"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="11"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
+      <c r="A34" s="16"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="23"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="29"/>
+      <c r="A35" s="16"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="23"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="11"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="29"/>
+      <c r="A36" s="16"/>
       <c r="B36" s="1"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="23"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="29"/>
+      <c r="A37" s="16"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="23"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="11"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="29"/>
+      <c r="A38" s="16"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="23"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="11"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="29"/>
+      <c r="A39" s="16"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="23"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="29"/>
+      <c r="A40" s="16"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="23"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="11"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="29"/>
+      <c r="A41" s="16"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="23"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="11"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="29"/>
+      <c r="A42" s="16"/>
       <c r="B42" s="1"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="23"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="11"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
+      <c r="A43" s="16"/>
       <c r="B43" s="1"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="23"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="11"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
+      <c r="A44" s="16"/>
       <c r="B44" s="1"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="23"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="11"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
+      <c r="A45" s="16"/>
       <c r="B45" s="1"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="23"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="11"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="29"/>
+      <c r="A46" s="16"/>
       <c r="B46" s="1"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="23"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="11"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
+      <c r="A47" s="16"/>
       <c r="B47" s="1"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="23"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="11"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="29"/>
+      <c r="A48" s="16"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="23"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="11"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
+      <c r="A49" s="16"/>
       <c r="B49" s="1"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="23"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="11"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="29"/>
+      <c r="A50" s="16"/>
       <c r="B50" s="1"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="23"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="11"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
+      <c r="A51" s="16"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="23"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="11"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="29"/>
+      <c r="A52" s="16"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="23"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="11"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="29"/>
+      <c r="A53" s="16"/>
       <c r="B53" s="1"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="23"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="11"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="29"/>
+      <c r="A54" s="16"/>
       <c r="B54" s="1"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="23"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="11"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="29"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="1"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="23"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="11"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="29"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
-      <c r="M56" s="7"/>
-      <c r="N56" s="23"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="11"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="29"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="1"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="23"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="11"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="29"/>
+      <c r="A58" s="16"/>
       <c r="B58" s="1"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="23"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="11"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="29"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
-      <c r="N59" s="23"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="11"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="29"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="1"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
-      <c r="N60" s="23"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="11"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="29"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
-      <c r="N61" s="23"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="11"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="29"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="23"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="11"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="29"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
-      <c r="N63" s="23"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="11"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="29"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="23"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="11"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="29"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
-      <c r="N65" s="23"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="11"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="29"/>
+      <c r="A66" s="16"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="7"/>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="23"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="11"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="29"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7"/>
-      <c r="M67" s="7"/>
-      <c r="N67" s="23"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="11"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="29"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="23"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="11"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="29"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
-      <c r="N69" s="23"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="11"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="29"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="1"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="23"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="11"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="29"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
-      <c r="M71" s="7"/>
-      <c r="N71" s="23"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="11"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="29"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="23"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="11"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="29"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
-      <c r="K73" s="7"/>
-      <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
-      <c r="N73" s="23"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="11"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="29"/>
+      <c r="A74" s="16"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="23"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="11"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="29"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
-      <c r="N75" s="23"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="11"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="29"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="1"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="23"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="11"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="29"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
-      <c r="N77" s="23"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="11"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="29"/>
+      <c r="A78" s="16"/>
       <c r="B78" s="1"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
-      <c r="N78" s="23"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="11"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="29"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="7"/>
-      <c r="K79" s="7"/>
-      <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
-      <c r="N79" s="23"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="11"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="29"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="1"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="23"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="11"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="29"/>
+      <c r="A81" s="16"/>
       <c r="B81" s="1"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
-      <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="23"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="11"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="29"/>
+      <c r="A82" s="16"/>
       <c r="B82" s="1"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
-      <c r="K82" s="7"/>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="23"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="11"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="29"/>
+      <c r="A83" s="16"/>
       <c r="B83" s="1"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="7"/>
-      <c r="K83" s="7"/>
-      <c r="L83" s="7"/>
-      <c r="M83" s="7"/>
-      <c r="N83" s="23"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="11"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="29"/>
+      <c r="A84" s="16"/>
       <c r="B84" s="1"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-      <c r="I84" s="7"/>
-      <c r="J84" s="7"/>
-      <c r="K84" s="7"/>
-      <c r="L84" s="7"/>
-      <c r="M84" s="7"/>
-      <c r="N84" s="23"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="11"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="29"/>
+      <c r="A85" s="16"/>
       <c r="B85" s="1"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
-      <c r="K85" s="7"/>
-      <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
-      <c r="N85" s="23"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="11"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="29"/>
+      <c r="A86" s="16"/>
       <c r="B86" s="1"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
-      <c r="I86" s="7"/>
-      <c r="J86" s="7"/>
-      <c r="K86" s="7"/>
-      <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
-      <c r="N86" s="23"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="11"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="29"/>
+      <c r="A87" s="16"/>
       <c r="B87" s="1"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7"/>
-      <c r="J87" s="7"/>
-      <c r="K87" s="7"/>
-      <c r="L87" s="7"/>
-      <c r="M87" s="7"/>
-      <c r="N87" s="23"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="11"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="29"/>
+      <c r="A88" s="16"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7"/>
-      <c r="J88" s="7"/>
-      <c r="K88" s="7"/>
-      <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
-      <c r="N88" s="23"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="11"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="29"/>
+      <c r="A89" s="16"/>
       <c r="B89" s="1"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
-      <c r="N89" s="23"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="11"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="29"/>
+      <c r="A90" s="16"/>
       <c r="B90" s="1"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-      <c r="H90" s="7"/>
-      <c r="I90" s="7"/>
-      <c r="J90" s="7"/>
-      <c r="K90" s="7"/>
-      <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
-      <c r="N90" s="23"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="11"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="29"/>
+      <c r="A91" s="16"/>
       <c r="B91" s="1"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="7"/>
-      <c r="K91" s="7"/>
-      <c r="L91" s="7"/>
-      <c r="M91" s="7"/>
-      <c r="N91" s="23"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="11"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="29"/>
+      <c r="A92" s="16"/>
       <c r="B92" s="1"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7"/>
-      <c r="J92" s="7"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
-      <c r="N92" s="23"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="11"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="29"/>
+      <c r="A93" s="16"/>
       <c r="B93" s="1"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
-      <c r="K93" s="7"/>
-      <c r="L93" s="7"/>
-      <c r="M93" s="7"/>
-      <c r="N93" s="23"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="11"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="29"/>
+      <c r="A94" s="16"/>
       <c r="B94" s="1"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="7"/>
-      <c r="K94" s="7"/>
-      <c r="L94" s="7"/>
-      <c r="M94" s="7"/>
-      <c r="N94" s="23"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="11"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="29"/>
+      <c r="A95" s="16"/>
       <c r="B95" s="1"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="7"/>
-      <c r="K95" s="7"/>
-      <c r="L95" s="7"/>
-      <c r="M95" s="7"/>
-      <c r="N95" s="23"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="11"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="29"/>
+      <c r="A96" s="16"/>
       <c r="B96" s="1"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7"/>
-      <c r="J96" s="7"/>
-      <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
-      <c r="N96" s="23"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
+      <c r="M96" s="6"/>
+      <c r="N96" s="11"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="29"/>
+      <c r="A97" s="16"/>
       <c r="B97" s="1"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7"/>
-      <c r="J97" s="7"/>
-      <c r="K97" s="7"/>
-      <c r="L97" s="7"/>
-      <c r="M97" s="7"/>
-      <c r="N97" s="23"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="11"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="29"/>
+      <c r="A98" s="16"/>
       <c r="B98" s="1"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
-      <c r="I98" s="7"/>
-      <c r="J98" s="7"/>
-      <c r="K98" s="7"/>
-      <c r="L98" s="7"/>
-      <c r="M98" s="7"/>
-      <c r="N98" s="23"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="11"/>
     </row>
     <row r="99" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="30"/>
-      <c r="B99" s="16"/>
-      <c r="C99" s="24"/>
-      <c r="D99" s="24"/>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="24"/>
-      <c r="H99" s="24"/>
-      <c r="I99" s="24"/>
-      <c r="J99" s="24"/>
-      <c r="K99" s="24"/>
-      <c r="L99" s="24"/>
-      <c r="M99" s="24"/>
-      <c r="N99" s="25"/>
+      <c r="A99" s="17"/>
+      <c r="B99" s="10"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12"/>
+      <c r="M99" s="12"/>
+      <c r="N99" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/01.Documentation/Control de versiones de Sistema.xlsx
+++ b/01.Documentation/Control de versiones de Sistema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Team Dropbox\JRODRIGUEZ\Repositorios\01.Rover\01.Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB364415-99B6-497E-A661-4474EDC44A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159FE98A-6F96-4990-B698-11DF2E9B2671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
   </bookViews>
   <sheets>
     <sheet name="ROVER" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="81">
   <si>
     <t>Cambios</t>
   </si>
@@ -442,7 +442,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -560,17 +560,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -578,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -640,9 +629,6 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -652,6 +638,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -661,6 +668,15 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -687,27 +703,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1023,263 +1018,278 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BF0786-E6C7-4307-9339-45491EF3032D}">
-  <dimension ref="A1:S100"/>
+  <dimension ref="A1:T100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="44.85546875" style="39" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="2" customWidth="1"/>
-    <col min="4" max="6" width="12.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="44.85546875" style="28" customWidth="1"/>
+    <col min="3" max="4" width="17.5703125" style="2" customWidth="1"/>
+    <col min="5" max="7" width="12.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="30" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" spans="1:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+    </row>
+    <row r="2" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="32" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="32" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="32" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="24"/>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="B6" s="30"/>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="35" t="s">
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="33" t="s">
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="28" t="s">
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="41"/>
+    <row r="9" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="16" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="F9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="G9" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="H9" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="J9" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="K9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="L9" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="M9" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="N9" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="O9" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="O9" s="17" t="s">
+      <c r="P9" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="Q9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="18" t="s">
+      <c r="R9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="R9" s="18" t="s">
+      <c r="S9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="S9" s="29"/>
-    </row>
-    <row r="10" spans="1:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="42"/>
+      <c r="T9" s="38"/>
+    </row>
+    <row r="10" spans="1:20" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="33"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="4">
-        <f>MAX(C11:C37)</f>
+        <f>MAX(C11:C100)</f>
+        <v>400</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" ref="D10:H10" si="0">MAX(D11:D100)</f>
         <v>125</v>
-      </c>
-      <c r="D10" s="4">
-        <f t="shared" ref="D10:E10" si="0">MAX(D11:D37)</f>
-        <v>313</v>
       </c>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
+        <v>313</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="4">
-        <f>MAX(F11:F37)</f>
+      <c r="G10" s="4">
+        <f t="shared" si="0"/>
         <v>205</v>
       </c>
-      <c r="G10" s="5">
-        <f>MAX(G11:G100)</f>
+      <c r="H10" s="5">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="H10" s="5">
-        <f t="shared" ref="H10:O10" si="1">MAX(H11:H100)</f>
+      <c r="I10" s="5">
+        <f t="shared" ref="I10" si="1">MAX(I11:I100)</f>
         <v>6</v>
       </c>
-      <c r="I10" s="5">
-        <f t="shared" si="1"/>
+      <c r="J10" s="5">
+        <f t="shared" ref="J10" si="2">MAX(J11:J100)</f>
         <v>3</v>
       </c>
-      <c r="J10" s="5">
-        <f t="shared" si="1"/>
+      <c r="K10" s="5">
+        <f t="shared" ref="K10:L10" si="3">MAX(K11:K100)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="22">
-        <f t="shared" si="1"/>
+      <c r="L10" s="5">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="L10" s="5">
-        <f t="shared" si="1"/>
+      <c r="M10" s="5">
+        <f t="shared" ref="M10" si="4">MAX(M11:M100)</f>
         <v>1</v>
       </c>
-      <c r="M10" s="5">
-        <f t="shared" si="1"/>
+      <c r="N10" s="5">
+        <f t="shared" ref="N10" si="5">MAX(N11:N100)</f>
         <v>3</v>
       </c>
-      <c r="N10" s="5">
-        <f t="shared" si="1"/>
+      <c r="O10" s="5">
+        <f t="shared" ref="O10" si="6">MAX(O11:O100)</f>
         <v>7</v>
       </c>
-      <c r="O10" s="5">
-        <f t="shared" si="1"/>
+      <c r="P10" s="5">
+        <f t="shared" ref="P10:Q10" si="7">MAX(P11:P100)</f>
         <v>1</v>
       </c>
-      <c r="P10" s="6">
-        <f>MAX(P11:P100)</f>
+      <c r="Q10" s="6">
+        <f>MAX(Q11:Q100)</f>
         <v>5</v>
       </c>
-      <c r="Q10" s="6">
-        <f t="shared" ref="Q10:R10" si="2">MAX(Q11:Q100)</f>
+      <c r="R10" s="6">
+        <f t="shared" ref="R10:S10" si="8">MAX(R11:R100)</f>
         <v>11</v>
       </c>
-      <c r="R10" s="6">
-        <f t="shared" si="2"/>
+      <c r="S10" s="6">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="S10" s="15"/>
-    </row>
-    <row r="11" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T10" s="15"/>
+    </row>
+    <row r="11" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1292,21 +1302,24 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
-      <c r="S11" s="7"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S11" s="1"/>
+      <c r="T11" s="7"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1319,21 +1332,24 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
-      <c r="S12" s="7"/>
-    </row>
-    <row r="13" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="S12" s="1"/>
+      <c r="T12" s="7"/>
+    </row>
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1346,77 +1362,81 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="7"/>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S13" s="1"/>
+      <c r="T13" s="7"/>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="13">
-        <v>121</v>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D14" s="13">
         <v>121</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="13">
+        <v>121</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1">
-        <v>5</v>
+      <c r="G14" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="H14" s="1">
         <v>5</v>
       </c>
       <c r="I14" s="1">
+        <v>5</v>
+      </c>
+      <c r="J14" s="1">
         <v>2</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>1</v>
       </c>
-      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="1">
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1">
         <v>5</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="R14" s="1">
         <v>9</v>
       </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
         <v>10</v>
       </c>
-      <c r="S14" s="7"/>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T14" s="7"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="13">
+      <c r="G15" s="13">
         <v>201</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1426,41 +1446,44 @@
       <c r="J15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S15" s="7"/>
-    </row>
-    <row r="16" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="S15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T15" s="7"/>
+    </row>
+    <row r="16" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1473,41 +1496,44 @@
       <c r="J16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-      <c r="P16" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S16" s="7"/>
-    </row>
-    <row r="17" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="S16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T16" s="7"/>
+    </row>
+    <row r="17" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1520,41 +1546,44 @@
       <c r="J17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P17" s="1"/>
       <c r="Q17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S17" s="7"/>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T17" s="7"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="13">
-        <v>122</v>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D18" s="13">
         <v>122</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="13">
+        <v>122</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1567,27 +1596,30 @@
       <c r="J18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-      <c r="P18" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P18" s="1"/>
       <c r="Q18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S18" s="7"/>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T18" s="7"/>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1597,14 +1629,14 @@
         <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="13">
+      <c r="G19" s="13">
         <v>202</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1614,41 +1646,44 @@
       <c r="J19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-      <c r="P19" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P19" s="1"/>
       <c r="Q19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S19" s="7"/>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T19" s="7"/>
+    </row>
+    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="13">
-        <v>123</v>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D20" s="13">
         <v>123</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="13">
+        <v>123</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G20" s="1" t="s">
         <v>13</v>
       </c>
@@ -1661,27 +1696,30 @@
       <c r="J20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="P20" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S20" s="7"/>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T20" s="7"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -1691,14 +1729,14 @@
         <v>13</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="13">
+      <c r="G21" s="13">
         <v>203</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
       </c>
@@ -1708,42 +1746,45 @@
       <c r="J21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-      <c r="P21" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S21" s="7"/>
-    </row>
-    <row r="22" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="S21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T21" s="7"/>
+    </row>
+    <row r="22" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="14">
         <v>310</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H22" s="1" t="s">
@@ -1755,74 +1796,80 @@
       <c r="J22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-      <c r="P22" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S22" s="7"/>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T22" s="7"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="13">
         <v>123</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="13">
+      <c r="G23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="13">
         <v>6</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-      <c r="P23" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R23" s="13">
+      <c r="R23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S23" s="13">
         <v>11</v>
       </c>
-      <c r="S23" s="7"/>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T23" s="7"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -1832,105 +1879,111 @@
         <v>13</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="13">
+      <c r="G24" s="13">
         <v>203</v>
       </c>
-      <c r="G24" s="13">
+      <c r="H24" s="13">
         <v>6</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-      <c r="P24" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S24" s="7"/>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T24" s="7"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="14">
+      <c r="C25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="14">
         <v>310</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="13">
+      <c r="G25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="13">
         <v>6</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-      <c r="P25" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S25" s="7"/>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T25" s="7"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="13">
         <v>124</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G26" s="1" t="s">
         <v>13</v>
       </c>
@@ -1943,27 +1996,30 @@
       <c r="J26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-      <c r="P26" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S26" s="7"/>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T26" s="7"/>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -1973,14 +2029,14 @@
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="13">
+      <c r="G27" s="13">
         <v>204</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
       </c>
@@ -1990,42 +2046,45 @@
       <c r="J27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-      <c r="P27" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S27" s="7"/>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T27" s="7"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="14">
         <v>311</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H28" s="1" t="s">
@@ -2037,42 +2096,45 @@
       <c r="J28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-      <c r="P28" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S28" s="7"/>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T28" s="7"/>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="C29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="14">
         <v>312</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H29" s="1" t="s">
@@ -2084,55 +2146,58 @@
       <c r="J29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-      <c r="P29" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S29" s="7"/>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T29" s="7"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="14">
         <v>125</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="E30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="14">
+      <c r="G30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="14">
         <v>6</v>
       </c>
-      <c r="I30" s="14">
+      <c r="J30" s="14">
         <v>3</v>
       </c>
-      <c r="J30" s="14">
+      <c r="K30" s="14">
         <v>1</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>22</v>
@@ -2146,50 +2211,53 @@
       <c r="O30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q30" s="3">
+      <c r="P30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R30" s="3">
         <v>10</v>
       </c>
-      <c r="R30" s="3">
+      <c r="S30" s="3">
         <v>12</v>
       </c>
-      <c r="S30" s="7"/>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T30" s="7"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F31" s="14">
+      <c r="G31" s="14">
         <v>205</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="14">
+      <c r="H31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="14">
         <v>6</v>
       </c>
-      <c r="I31" s="14">
+      <c r="J31" s="14">
         <v>3</v>
       </c>
-      <c r="J31" s="14">
+      <c r="K31" s="14">
         <v>1</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>22</v>
@@ -2203,50 +2271,53 @@
       <c r="O31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q31" s="3">
+      <c r="P31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R31" s="3">
         <v>10</v>
       </c>
-      <c r="R31" s="3">
+      <c r="S31" s="3">
         <v>12</v>
       </c>
-      <c r="S31" s="7"/>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T31" s="7"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="14">
+      <c r="C32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="14">
         <v>313</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="14">
+      <c r="G32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="14">
         <v>6</v>
       </c>
-      <c r="I32" s="14">
+      <c r="J32" s="14">
         <v>3</v>
       </c>
-      <c r="J32" s="14">
+      <c r="K32" s="14">
         <v>1</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>22</v>
@@ -2260,82 +2331,88 @@
       <c r="O32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R32" s="3">
         <v>10</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12</v>
       </c>
-      <c r="S32" s="7"/>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T32" s="7"/>
+    </row>
+    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="14">
         <v>125</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="E33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="14">
+      <c r="G33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="14">
         <v>6</v>
       </c>
-      <c r="I33" s="14">
+      <c r="J33" s="14">
         <v>3</v>
       </c>
-      <c r="J33" s="14">
+      <c r="K33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="14">
+      <c r="L33" s="14">
         <v>2</v>
       </c>
-      <c r="L33" s="14">
+      <c r="M33" s="14">
         <v>1</v>
       </c>
-      <c r="M33" s="14">
+      <c r="N33" s="14">
         <v>3</v>
       </c>
-      <c r="N33" s="14">
+      <c r="O33" s="14">
         <v>7</v>
       </c>
-      <c r="O33" s="14">
+      <c r="P33" s="14">
         <v>1</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R33" s="3">
         <v>10</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>12</v>
       </c>
-      <c r="S33" s="7"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33" s="7"/>
+    </row>
+    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -2347,12 +2424,12 @@
       <c r="F34" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="22">
         <v>8</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="I34" s="3" t="s">
         <v>13</v>
       </c>
@@ -2380,19 +2457,22 @@
       <c r="Q34" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R34" s="3">
-        <v>13</v>
-      </c>
-      <c r="S34" s="7"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S34" s="3">
+        <v>13</v>
+      </c>
+      <c r="T34" s="7"/>
+    </row>
+    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -2404,12 +2484,12 @@
       <c r="F35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="22">
         <v>8</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>13</v>
       </c>
@@ -2437,19 +2517,22 @@
       <c r="Q35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R35" s="3">
-        <v>13</v>
-      </c>
-      <c r="S35" s="7"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S35" s="3">
+        <v>13</v>
+      </c>
+      <c r="T35" s="7"/>
+    </row>
+    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -2461,12 +2544,12 @@
       <c r="F36" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="22">
         <v>8</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="I36" s="3" t="s">
         <v>13</v>
       </c>
@@ -2494,19 +2577,22 @@
       <c r="Q36" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R36" s="3">
-        <v>13</v>
-      </c>
-      <c r="S36" s="7"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S36" s="3">
+        <v>13</v>
+      </c>
+      <c r="T36" s="7"/>
+    </row>
+    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -2518,12 +2604,12 @@
       <c r="F37" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="22">
         <v>8</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="I37" s="3" t="s">
         <v>13</v>
       </c>
@@ -2551,19 +2637,22 @@
       <c r="Q37" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R37" s="3">
-        <v>13</v>
-      </c>
-      <c r="S37" s="7"/>
-    </row>
-    <row r="38" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="R37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S37" s="3">
+        <v>13</v>
+      </c>
+      <c r="T37" s="7"/>
+    </row>
+    <row r="38" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -2605,22 +2694,25 @@
       <c r="P38" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q38" s="23">
+      <c r="Q38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R38" s="22">
         <v>11</v>
       </c>
-      <c r="R38" s="23">
+      <c r="S38" s="22">
         <v>14</v>
       </c>
-      <c r="S38" s="7"/>
-    </row>
-    <row r="39" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T38" s="7"/>
+    </row>
+    <row r="39" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="37" t="s">
+      <c r="B39" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -2662,22 +2754,25 @@
       <c r="P39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q39" s="23">
+      <c r="Q39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R39" s="22">
         <v>11</v>
       </c>
-      <c r="R39" s="23">
+      <c r="S39" s="22">
         <v>14</v>
       </c>
-      <c r="S39" s="7"/>
-    </row>
-    <row r="40" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T39" s="7"/>
+    </row>
+    <row r="40" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -2719,23 +2814,26 @@
       <c r="P40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q40" s="23">
+      <c r="Q40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R40" s="22">
         <v>11</v>
       </c>
-      <c r="R40" s="23">
+      <c r="S40" s="22">
         <v>14</v>
       </c>
-      <c r="S40" s="7"/>
-    </row>
-    <row r="41" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T40" s="7"/>
+    </row>
+    <row r="41" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="37" t="s">
+      <c r="B41" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>13</v>
+      <c r="C41" s="22">
+        <v>400</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>13</v>
@@ -2776,17 +2874,20 @@
       <c r="P41" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q41" s="23">
+      <c r="Q41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R41" s="22">
         <v>11</v>
       </c>
-      <c r="R41" s="23">
+      <c r="S41" s="22">
         <v>14</v>
       </c>
-      <c r="S41" s="7"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T41" s="7"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
-      <c r="B42" s="37"/>
+      <c r="B42" s="26"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -2803,11 +2904,12 @@
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
-      <c r="S42" s="7"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S42" s="3"/>
+      <c r="T42" s="7"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
-      <c r="B43" s="37"/>
+      <c r="B43" s="26"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -2824,11 +2926,12 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
-      <c r="S43" s="7"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S43" s="3"/>
+      <c r="T43" s="7"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
-      <c r="B44" s="37"/>
+      <c r="B44" s="26"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -2845,11 +2948,12 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
-      <c r="S44" s="7"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S44" s="3"/>
+      <c r="T44" s="7"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
-      <c r="B45" s="37"/>
+      <c r="B45" s="26"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -2866,11 +2970,12 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
-      <c r="S45" s="7"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S45" s="3"/>
+      <c r="T45" s="7"/>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
-      <c r="B46" s="37"/>
+      <c r="B46" s="26"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -2887,11 +2992,12 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
-      <c r="S46" s="7"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S46" s="3"/>
+      <c r="T46" s="7"/>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
-      <c r="B47" s="37"/>
+      <c r="B47" s="26"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -2908,11 +3014,12 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
-      <c r="S47" s="7"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S47" s="3"/>
+      <c r="T47" s="7"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
-      <c r="B48" s="37"/>
+      <c r="B48" s="26"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2929,11 +3036,12 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
-      <c r="S48" s="7"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S48" s="3"/>
+      <c r="T48" s="7"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
-      <c r="B49" s="37"/>
+      <c r="B49" s="26"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -2950,11 +3058,12 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
-      <c r="S49" s="7"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S49" s="3"/>
+      <c r="T49" s="7"/>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
-      <c r="B50" s="37"/>
+      <c r="B50" s="26"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -2971,11 +3080,12 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
-      <c r="S50" s="7"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S50" s="3"/>
+      <c r="T50" s="7"/>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
-      <c r="B51" s="37"/>
+      <c r="B51" s="26"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -2992,11 +3102,12 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
-      <c r="S51" s="7"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S51" s="3"/>
+      <c r="T51" s="7"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
-      <c r="B52" s="37"/>
+      <c r="B52" s="26"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -3013,11 +3124,12 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
-      <c r="S52" s="7"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S52" s="3"/>
+      <c r="T52" s="7"/>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
-      <c r="B53" s="37"/>
+      <c r="B53" s="26"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3034,11 +3146,12 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
-      <c r="S53" s="7"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S53" s="3"/>
+      <c r="T53" s="7"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
-      <c r="B54" s="37"/>
+      <c r="B54" s="26"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -3055,11 +3168,12 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
-      <c r="S54" s="7"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S54" s="3"/>
+      <c r="T54" s="7"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
-      <c r="B55" s="37"/>
+      <c r="B55" s="26"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -3076,11 +3190,12 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-      <c r="S55" s="7"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S55" s="3"/>
+      <c r="T55" s="7"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
-      <c r="B56" s="37"/>
+      <c r="B56" s="26"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -3097,11 +3212,12 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-      <c r="S56" s="7"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S56" s="3"/>
+      <c r="T56" s="7"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
-      <c r="B57" s="37"/>
+      <c r="B57" s="26"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -3118,11 +3234,12 @@
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
-      <c r="S57" s="7"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S57" s="3"/>
+      <c r="T57" s="7"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
-      <c r="B58" s="37"/>
+      <c r="B58" s="26"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -3139,11 +3256,12 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
-      <c r="S58" s="7"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S58" s="3"/>
+      <c r="T58" s="7"/>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
-      <c r="B59" s="37"/>
+      <c r="B59" s="26"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -3160,11 +3278,12 @@
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
-      <c r="S59" s="7"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S59" s="3"/>
+      <c r="T59" s="7"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
-      <c r="B60" s="37"/>
+      <c r="B60" s="26"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -3181,11 +3300,12 @@
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
-      <c r="S60" s="7"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S60" s="3"/>
+      <c r="T60" s="7"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
-      <c r="B61" s="37"/>
+      <c r="B61" s="26"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -3202,11 +3322,12 @@
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
-      <c r="S61" s="7"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S61" s="3"/>
+      <c r="T61" s="7"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
-      <c r="B62" s="37"/>
+      <c r="B62" s="26"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -3223,11 +3344,12 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
-      <c r="S62" s="7"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S62" s="3"/>
+      <c r="T62" s="7"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
-      <c r="B63" s="37"/>
+      <c r="B63" s="26"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3244,11 +3366,12 @@
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
-      <c r="S63" s="7"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S63" s="3"/>
+      <c r="T63" s="7"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
-      <c r="B64" s="37"/>
+      <c r="B64" s="26"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -3265,11 +3388,12 @@
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
-      <c r="S64" s="7"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S64" s="3"/>
+      <c r="T64" s="7"/>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
-      <c r="B65" s="37"/>
+      <c r="B65" s="26"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3286,11 +3410,12 @@
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
-      <c r="S65" s="7"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S65" s="3"/>
+      <c r="T65" s="7"/>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
-      <c r="B66" s="37"/>
+      <c r="B66" s="26"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3307,11 +3432,12 @@
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
-      <c r="S66" s="7"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S66" s="3"/>
+      <c r="T66" s="7"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
-      <c r="B67" s="37"/>
+      <c r="B67" s="26"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3328,11 +3454,12 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-      <c r="S67" s="7"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S67" s="3"/>
+      <c r="T67" s="7"/>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
-      <c r="B68" s="37"/>
+      <c r="B68" s="26"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3349,11 +3476,12 @@
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
-      <c r="S68" s="7"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S68" s="3"/>
+      <c r="T68" s="7"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
-      <c r="B69" s="37"/>
+      <c r="B69" s="26"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -3370,11 +3498,12 @@
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
-      <c r="S69" s="7"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S69" s="3"/>
+      <c r="T69" s="7"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
-      <c r="B70" s="37"/>
+      <c r="B70" s="26"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -3391,11 +3520,12 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
-      <c r="S70" s="7"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S70" s="3"/>
+      <c r="T70" s="7"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
-      <c r="B71" s="37"/>
+      <c r="B71" s="26"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -3412,11 +3542,12 @@
       <c r="P71" s="3"/>
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
-      <c r="S71" s="7"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S71" s="3"/>
+      <c r="T71" s="7"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="11"/>
-      <c r="B72" s="37"/>
+      <c r="B72" s="26"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -3433,11 +3564,12 @@
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
-      <c r="S72" s="7"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S72" s="3"/>
+      <c r="T72" s="7"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="11"/>
-      <c r="B73" s="37"/>
+      <c r="B73" s="26"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -3454,11 +3586,12 @@
       <c r="P73" s="3"/>
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
-      <c r="S73" s="7"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S73" s="3"/>
+      <c r="T73" s="7"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="11"/>
-      <c r="B74" s="37"/>
+      <c r="B74" s="26"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -3475,11 +3608,12 @@
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
-      <c r="S74" s="7"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S74" s="3"/>
+      <c r="T74" s="7"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="11"/>
-      <c r="B75" s="37"/>
+      <c r="B75" s="26"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -3496,11 +3630,12 @@
       <c r="P75" s="3"/>
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
-      <c r="S75" s="7"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S75" s="3"/>
+      <c r="T75" s="7"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="11"/>
-      <c r="B76" s="37"/>
+      <c r="B76" s="26"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3517,11 +3652,12 @@
       <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
-      <c r="S76" s="7"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S76" s="3"/>
+      <c r="T76" s="7"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="11"/>
-      <c r="B77" s="37"/>
+      <c r="B77" s="26"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3538,11 +3674,12 @@
       <c r="P77" s="3"/>
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
-      <c r="S77" s="7"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S77" s="3"/>
+      <c r="T77" s="7"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
-      <c r="B78" s="37"/>
+      <c r="B78" s="26"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -3559,11 +3696,12 @@
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
-      <c r="S78" s="7"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S78" s="3"/>
+      <c r="T78" s="7"/>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="11"/>
-      <c r="B79" s="37"/>
+      <c r="B79" s="26"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -3580,11 +3718,12 @@
       <c r="P79" s="3"/>
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
-      <c r="S79" s="7"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S79" s="3"/>
+      <c r="T79" s="7"/>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="11"/>
-      <c r="B80" s="37"/>
+      <c r="B80" s="26"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -3601,11 +3740,12 @@
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
-      <c r="S80" s="7"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S80" s="3"/>
+      <c r="T80" s="7"/>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="11"/>
-      <c r="B81" s="37"/>
+      <c r="B81" s="26"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -3622,11 +3762,12 @@
       <c r="P81" s="3"/>
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
-      <c r="S81" s="7"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S81" s="3"/>
+      <c r="T81" s="7"/>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="11"/>
-      <c r="B82" s="37"/>
+      <c r="B82" s="26"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -3643,11 +3784,12 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-      <c r="S82" s="7"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S82" s="3"/>
+      <c r="T82" s="7"/>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="11"/>
-      <c r="B83" s="37"/>
+      <c r="B83" s="26"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -3664,11 +3806,12 @@
       <c r="P83" s="3"/>
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
-      <c r="S83" s="7"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S83" s="3"/>
+      <c r="T83" s="7"/>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="11"/>
-      <c r="B84" s="37"/>
+      <c r="B84" s="26"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -3685,11 +3828,12 @@
       <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
-      <c r="S84" s="7"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S84" s="3"/>
+      <c r="T84" s="7"/>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="11"/>
-      <c r="B85" s="37"/>
+      <c r="B85" s="26"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -3706,11 +3850,12 @@
       <c r="P85" s="3"/>
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
-      <c r="S85" s="7"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S85" s="3"/>
+      <c r="T85" s="7"/>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="11"/>
-      <c r="B86" s="37"/>
+      <c r="B86" s="26"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -3727,11 +3872,12 @@
       <c r="P86" s="3"/>
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
-      <c r="S86" s="7"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S86" s="3"/>
+      <c r="T86" s="7"/>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="11"/>
-      <c r="B87" s="37"/>
+      <c r="B87" s="26"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -3748,11 +3894,12 @@
       <c r="P87" s="3"/>
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
-      <c r="S87" s="7"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S87" s="3"/>
+      <c r="T87" s="7"/>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="11"/>
-      <c r="B88" s="37"/>
+      <c r="B88" s="26"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -3769,11 +3916,12 @@
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
-      <c r="S88" s="7"/>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S88" s="3"/>
+      <c r="T88" s="7"/>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="11"/>
-      <c r="B89" s="37"/>
+      <c r="B89" s="26"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -3790,11 +3938,12 @@
       <c r="P89" s="3"/>
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
-      <c r="S89" s="7"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S89" s="3"/>
+      <c r="T89" s="7"/>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="11"/>
-      <c r="B90" s="37"/>
+      <c r="B90" s="26"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -3811,11 +3960,12 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-      <c r="S90" s="7"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S90" s="3"/>
+      <c r="T90" s="7"/>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="11"/>
-      <c r="B91" s="37"/>
+      <c r="B91" s="26"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -3832,11 +3982,12 @@
       <c r="P91" s="3"/>
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
-      <c r="S91" s="7"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S91" s="3"/>
+      <c r="T91" s="7"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="11"/>
-      <c r="B92" s="37"/>
+      <c r="B92" s="26"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -3853,11 +4004,12 @@
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
-      <c r="S92" s="7"/>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S92" s="3"/>
+      <c r="T92" s="7"/>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="11"/>
-      <c r="B93" s="37"/>
+      <c r="B93" s="26"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -3874,11 +4026,12 @@
       <c r="P93" s="3"/>
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
-      <c r="S93" s="7"/>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S93" s="3"/>
+      <c r="T93" s="7"/>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="11"/>
-      <c r="B94" s="37"/>
+      <c r="B94" s="26"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -3895,11 +4048,12 @@
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
-      <c r="S94" s="7"/>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S94" s="3"/>
+      <c r="T94" s="7"/>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="11"/>
-      <c r="B95" s="37"/>
+      <c r="B95" s="26"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -3916,11 +4070,12 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-      <c r="S95" s="7"/>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S95" s="3"/>
+      <c r="T95" s="7"/>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="11"/>
-      <c r="B96" s="37"/>
+      <c r="B96" s="26"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -3937,11 +4092,12 @@
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
-      <c r="S96" s="7"/>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S96" s="3"/>
+      <c r="T96" s="7"/>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="11"/>
-      <c r="B97" s="37"/>
+      <c r="B97" s="26"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -3958,11 +4114,12 @@
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
-      <c r="S97" s="7"/>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S97" s="3"/>
+      <c r="T97" s="7"/>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="11"/>
-      <c r="B98" s="37"/>
+      <c r="B98" s="26"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -3979,11 +4136,12 @@
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
-      <c r="S98" s="7"/>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S98" s="3"/>
+      <c r="T98" s="7"/>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="11"/>
-      <c r="B99" s="37"/>
+      <c r="B99" s="26"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -4000,11 +4158,12 @@
       <c r="P99" s="3"/>
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
-      <c r="S99" s="7"/>
-    </row>
-    <row r="100" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S99" s="3"/>
+      <c r="T99" s="7"/>
+    </row>
+    <row r="100" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="12"/>
-      <c r="B100" s="43"/>
+      <c r="B100" s="29"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
@@ -4021,27 +4180,28 @@
       <c r="P100" s="8"/>
       <c r="Q100" s="8"/>
       <c r="R100" s="8"/>
-      <c r="S100" s="9"/>
+      <c r="S100" s="8"/>
+      <c r="T100" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D3:G3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:B10"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:O8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="H8:P8"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/01.Documentation/Control de versiones de Sistema.xlsx
+++ b/01.Documentation/Control de versiones de Sistema.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Team Dropbox\JRODRIGUEZ\Repositorios\01.Rover\01.Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159FE98A-6F96-4990-B698-11DF2E9B2671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C2FD14-9605-4BB2-BCFD-7092E6DDD925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="86">
   <si>
     <t>Cambios</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>X</t>
-  </si>
-  <si>
-    <t>RCA/Universal</t>
   </si>
   <si>
     <t>Version
@@ -285,6 +282,24 @@
   <si>
     <t>HotFix Eliminacion Pull UP SWD en DCDC y 
 Fix R22 CPU no en BOM</t>
+  </si>
+  <si>
+    <t>5.0.0.0</t>
+  </si>
+  <si>
+    <t>RCA</t>
+  </si>
+  <si>
+    <t>Universal</t>
+  </si>
+  <si>
+    <t>Vantablack</t>
+  </si>
+  <si>
+    <t>Creacion del modelo Vantablack</t>
+  </si>
+  <si>
+    <t>VantaMachine</t>
   </si>
 </sst>
 </file>
@@ -567,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -656,8 +671,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -683,25 +716,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1018,266 +1036,288 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BF0786-E6C7-4307-9339-45491EF3032D}">
-  <dimension ref="A1:T100"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="10" customWidth="1"/>
     <col min="2" max="2" width="44.85546875" style="28" customWidth="1"/>
-    <col min="3" max="4" width="17.5703125" style="2" customWidth="1"/>
-    <col min="5" max="7" width="12.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.42578125" style="2"/>
+    <col min="3" max="5" width="17.5703125" style="2" customWidth="1"/>
+    <col min="6" max="8" width="12.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:22" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="39" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-    </row>
-    <row r="2" spans="1:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="40" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="41" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="30"/>
-    </row>
-    <row r="7" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="34" t="s">
+      <c r="B6" s="33"/>
+    </row>
+    <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44" t="s">
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="42" t="s">
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="35"/>
+      <c r="T8" s="45"/>
+      <c r="U8" s="45"/>
+      <c r="V8" s="43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="38"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="16" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="E9" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="G9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="H9" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="J9" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="K9" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="L9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="L9" s="21" t="s">
+      <c r="M9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="O9" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="P9" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="O9" s="17" t="s">
+      <c r="Q9" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="P9" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q9" s="18" t="s">
+      <c r="R9" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="S9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="R9" s="18" t="s">
+      <c r="T9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="S9" s="18" t="s">
+      <c r="U9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="T9" s="38"/>
-    </row>
-    <row r="10" spans="1:20" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="36"/>
+      <c r="V9" s="44"/>
+    </row>
+    <row r="10" spans="1:22" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="39"/>
+      <c r="B10" s="42"/>
       <c r="C10" s="4">
         <f>MAX(C11:C100)</f>
         <v>400</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" ref="D10:H10" si="0">MAX(D11:D100)</f>
+        <f>MAX(D11:D100)</f>
+        <v>500</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" ref="E10:I10" si="0">MAX(E11:E100)</f>
         <v>125</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <f t="shared" si="0"/>
         <v>313</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
         <f t="shared" si="0"/>
         <v>205</v>
       </c>
-      <c r="H10" s="5">
+      <c r="I10" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="I10" s="5">
-        <f t="shared" ref="I10" si="1">MAX(I11:I100)</f>
+      <c r="J10" s="5">
+        <f t="shared" ref="J10" si="1">MAX(J11:J100)</f>
         <v>6</v>
       </c>
-      <c r="J10" s="5">
-        <f t="shared" ref="J10" si="2">MAX(J11:J100)</f>
+      <c r="K10" s="5">
+        <f t="shared" ref="K10" si="2">MAX(K11:K100)</f>
         <v>3</v>
       </c>
-      <c r="K10" s="5">
-        <f t="shared" ref="K10:L10" si="3">MAX(K11:K100)</f>
+      <c r="L10" s="5">
+        <f t="shared" ref="L10:M10" si="3">MAX(L11:L100)</f>
         <v>1</v>
       </c>
-      <c r="L10" s="5">
+      <c r="M10" s="5">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="M10" s="5">
-        <f t="shared" ref="M10" si="4">MAX(M11:M100)</f>
+      <c r="N10" s="5">
+        <f t="shared" ref="N10" si="4">MAX(N11:N100)</f>
         <v>1</v>
       </c>
-      <c r="N10" s="5">
-        <f t="shared" ref="N10" si="5">MAX(N11:N100)</f>
+      <c r="O10" s="5">
+        <f t="shared" ref="O10" si="5">MAX(O11:O100)</f>
         <v>3</v>
       </c>
-      <c r="O10" s="5">
-        <f t="shared" ref="O10" si="6">MAX(O11:O100)</f>
+      <c r="P10" s="5">
+        <f t="shared" ref="P10" si="6">MAX(P11:P100)</f>
         <v>7</v>
       </c>
-      <c r="P10" s="5">
-        <f t="shared" ref="P10:Q10" si="7">MAX(P11:P100)</f>
+      <c r="Q10" s="5">
+        <f t="shared" ref="Q10:R10" si="7">MAX(Q11:Q100)</f>
         <v>1</v>
       </c>
-      <c r="Q10" s="6">
-        <f>MAX(Q11:Q100)</f>
+      <c r="R10" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S10" s="6">
+        <f>MAX(S11:S100)</f>
         <v>5</v>
       </c>
-      <c r="R10" s="6">
-        <f t="shared" ref="R10:S10" si="8">MAX(R11:R100)</f>
+      <c r="T10" s="6">
+        <f t="shared" ref="T10:U10" si="8">MAX(T11:T100)</f>
         <v>11</v>
       </c>
-      <c r="S10" s="6">
+      <c r="U10" s="6">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="T10" s="15"/>
-    </row>
-    <row r="11" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V10" s="15"/>
+    </row>
+    <row r="11" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>5</v>
@@ -1285,12 +1325,14 @@
       <c r="C11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -1303,11 +1345,13 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="7"/>
-    </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="7"/>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>6</v>
@@ -1315,12 +1359,14 @@
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1333,11 +1379,13 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="7"/>
-    </row>
-    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="7"/>
+    </row>
+    <row r="13" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>7</v>
@@ -1345,12 +1393,14 @@
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1363,11 +1413,13 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="7"/>
-    </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="7"/>
+    </row>
+    <row r="14" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>9</v>
@@ -1375,49 +1427,53 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="13">
-        <v>121</v>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E14" s="13">
         <v>121</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="13">
+        <v>121</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="1">
-        <v>5</v>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="I14" s="1">
         <v>5</v>
       </c>
       <c r="J14" s="1">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1">
         <v>2</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1">
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1">
         <v>5</v>
       </c>
-      <c r="R14" s="1">
+      <c r="T14" s="1">
         <v>9</v>
       </c>
-      <c r="S14" s="1">
+      <c r="U14" s="1">
         <v>10</v>
       </c>
-      <c r="T14" s="7"/>
-    </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V14" s="7"/>
+    </row>
+    <row r="15" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>8</v>
@@ -1425,21 +1481,21 @@
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="13">
+      <c r="H15" s="13">
         <v>201</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1449,25 +1505,29 @@
       <c r="K15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
       <c r="S15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T15" s="7"/>
-    </row>
-    <row r="16" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" s="7"/>
+    </row>
+    <row r="16" spans="1:22" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="27" t="s">
         <v>18</v>
@@ -1475,18 +1535,18 @@
       <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1499,25 +1559,29 @@
       <c r="K16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
       <c r="S16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T16" s="7"/>
-    </row>
-    <row r="17" spans="1:20" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V16" s="7"/>
+    </row>
+    <row r="17" spans="1:22" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="27" t="s">
         <v>18</v>
@@ -1525,18 +1589,18 @@
       <c r="C17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1549,25 +1613,29 @@
       <c r="K17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
       <c r="S17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T17" s="7"/>
-    </row>
-    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V17" s="7"/>
+    </row>
+    <row r="18" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>19</v>
@@ -1575,18 +1643,18 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="13">
-        <v>122</v>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E18" s="13">
         <v>122</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="13">
+        <v>122</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1599,25 +1667,29 @@
       <c r="K18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-      <c r="Q18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
       <c r="S18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T18" s="7"/>
-    </row>
-    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18" s="7"/>
+    </row>
+    <row r="19" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>19</v>
@@ -1632,14 +1704,14 @@
         <v>13</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="13">
+      <c r="H19" s="13">
         <v>202</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1649,44 +1721,48 @@
       <c r="K19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
       <c r="S19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T19" s="7"/>
-    </row>
-    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V19" s="7"/>
+    </row>
+    <row r="20" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="13">
-        <v>123</v>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E20" s="13">
         <v>123</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="13">
+        <v>123</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
       </c>
@@ -1699,28 +1775,32 @@
       <c r="K20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
       <c r="S20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T20" s="7"/>
-    </row>
-    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V20" s="7"/>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>13</v>
@@ -1732,14 +1812,14 @@
         <v>13</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="13">
+      <c r="H21" s="13">
         <v>203</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
       </c>
@@ -1749,45 +1829,49 @@
       <c r="K21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
       <c r="S21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T21" s="7"/>
-    </row>
-    <row r="22" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+      <c r="T21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V21" s="7"/>
+    </row>
+    <row r="22" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>49</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="14">
+      <c r="D22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="14">
         <v>310</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -1799,78 +1883,86 @@
       <c r="K22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
       <c r="S22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T22" s="7"/>
-    </row>
-    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="7"/>
+    </row>
+    <row r="23" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13">
         <v>123</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="13">
+      <c r="H23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="13">
         <v>6</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="J23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S23" s="13">
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U23" s="13">
         <v>11</v>
       </c>
-      <c r="T23" s="7"/>
-    </row>
-    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V23" s="7"/>
+    </row>
+    <row r="24" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>13</v>
@@ -1882,111 +1974,119 @@
         <v>13</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="13">
+      <c r="H24" s="13">
         <v>203</v>
       </c>
-      <c r="H24" s="13">
+      <c r="I24" s="13">
         <v>6</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="J24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
       <c r="S24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T24" s="7"/>
-    </row>
-    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V24" s="7"/>
+    </row>
+    <row r="25" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="14">
+      <c r="D25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="14">
         <v>310</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="13">
+      <c r="H25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="13">
         <v>6</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="J25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
       <c r="S25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T25" s="7"/>
-    </row>
-    <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V25" s="7"/>
+    </row>
+    <row r="26" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13">
         <v>124</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
       </c>
@@ -1999,28 +2099,32 @@
       <c r="K26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
       <c r="S26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T26" s="7"/>
-    </row>
-    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V26" s="7"/>
+    </row>
+    <row r="27" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>13</v>
@@ -2032,14 +2136,14 @@
         <v>13</v>
       </c>
       <c r="F27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="13">
+      <c r="H27" s="13">
         <v>204</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,45 +2153,49 @@
       <c r="K27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
       <c r="S27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T27" s="7"/>
-    </row>
-    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V27" s="7"/>
+    </row>
+    <row r="28" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="D28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="14">
         <v>311</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2099,45 +2207,49 @@
       <c r="K28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L28" s="1"/>
+      <c r="L28" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
       <c r="S28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T28" s="7"/>
-    </row>
-    <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V28" s="7"/>
+    </row>
+    <row r="29" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="14">
+      <c r="D29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="14">
         <v>312</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2149,58 +2261,62 @@
       <c r="K29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
       <c r="S29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T29" s="7"/>
-    </row>
-    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="T29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V29" s="7"/>
+    </row>
+    <row r="30" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="14">
         <v>125</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="F30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="14">
+      <c r="H30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="14">
         <v>6</v>
       </c>
-      <c r="J30" s="14">
+      <c r="K30" s="14">
         <v>3</v>
       </c>
-      <c r="K30" s="14">
+      <c r="L30" s="14">
         <v>1</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>22</v>
@@ -2214,53 +2330,57 @@
       <c r="P30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Q30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R30" s="3">
+      <c r="Q30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R30" s="3"/>
+      <c r="S30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T30" s="3">
         <v>10</v>
       </c>
-      <c r="S30" s="3">
+      <c r="U30" s="3">
         <v>12</v>
       </c>
-      <c r="T30" s="7"/>
-    </row>
-    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V30" s="7"/>
+    </row>
+    <row r="31" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="14">
+      <c r="H31" s="14">
         <v>205</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="14">
+      <c r="I31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="14">
         <v>6</v>
       </c>
-      <c r="J31" s="14">
+      <c r="K31" s="14">
         <v>3</v>
       </c>
-      <c r="K31" s="14">
+      <c r="L31" s="14">
         <v>1</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>22</v>
@@ -2274,53 +2394,57 @@
       <c r="P31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Q31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R31" s="3">
+      <c r="Q31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R31" s="3"/>
+      <c r="S31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T31" s="3">
         <v>10</v>
       </c>
-      <c r="S31" s="3">
+      <c r="U31" s="3">
         <v>12</v>
       </c>
-      <c r="T31" s="7"/>
-    </row>
-    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V31" s="7"/>
+    </row>
+    <row r="32" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="26" t="s">
-        <v>70</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="14">
+      <c r="D32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="14">
         <v>313</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="14">
+      <c r="H32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="14">
         <v>6</v>
       </c>
-      <c r="J32" s="14">
+      <c r="K32" s="14">
         <v>3</v>
       </c>
-      <c r="K32" s="14">
+      <c r="L32" s="14">
         <v>1</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>22</v>
@@ -2334,508 +2458,544 @@
       <c r="P32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Q32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R32" s="3"/>
+      <c r="S32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T32" s="3">
         <v>10</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>12</v>
       </c>
-      <c r="T32" s="7"/>
-    </row>
-    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V32" s="7"/>
+    </row>
+    <row r="33" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="26" t="s">
-        <v>61</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="14">
         <v>125</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="F33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="14">
+      <c r="H33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="14">
         <v>6</v>
       </c>
-      <c r="J33" s="14">
+      <c r="K33" s="14">
         <v>3</v>
       </c>
-      <c r="K33" s="14">
+      <c r="L33" s="14">
         <v>1</v>
       </c>
-      <c r="L33" s="14">
+      <c r="M33" s="14">
         <v>2</v>
       </c>
-      <c r="M33" s="14">
+      <c r="N33" s="14">
         <v>1</v>
       </c>
-      <c r="N33" s="14">
+      <c r="O33" s="14">
         <v>3</v>
       </c>
-      <c r="O33" s="14">
+      <c r="P33" s="14">
         <v>7</v>
       </c>
-      <c r="P33" s="14">
+      <c r="Q33" s="14">
         <v>1</v>
       </c>
-      <c r="Q33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="14"/>
+      <c r="S33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T33" s="3">
         <v>10</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>12</v>
       </c>
-      <c r="T33" s="7"/>
-    </row>
-    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V33" s="7"/>
+    </row>
+    <row r="34" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="22">
+        <v>8</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U34" s="3">
+        <v>13</v>
+      </c>
+      <c r="V34" s="7"/>
+    </row>
+    <row r="35" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B35" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="22">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U35" s="3">
+        <v>13</v>
+      </c>
+      <c r="V35" s="7"/>
+    </row>
+    <row r="36" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="22">
+        <v>8</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U36" s="3">
+        <v>13</v>
+      </c>
+      <c r="V36" s="7"/>
+    </row>
+    <row r="37" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="22">
+        <v>8</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U37" s="3">
+        <v>13</v>
+      </c>
+      <c r="V37" s="7"/>
+    </row>
+    <row r="38" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="22">
-        <v>8</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S34" s="3">
-        <v>13</v>
-      </c>
-      <c r="T34" s="7"/>
-    </row>
-    <row r="35" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H35" s="22">
-        <v>8</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S35" s="3">
-        <v>13</v>
-      </c>
-      <c r="T35" s="7"/>
-    </row>
-    <row r="36" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" s="22">
-        <v>8</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S36" s="3">
-        <v>13</v>
-      </c>
-      <c r="T36" s="7"/>
-    </row>
-    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" s="22">
-        <v>8</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S37" s="3">
-        <v>13</v>
-      </c>
-      <c r="T37" s="7"/>
-    </row>
-    <row r="38" spans="1:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
+      <c r="B38" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T38" s="22">
+        <v>11</v>
+      </c>
+      <c r="U38" s="22">
+        <v>14</v>
+      </c>
+      <c r="V38" s="7"/>
+    </row>
+    <row r="39" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R38" s="22">
+      <c r="B39" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T39" s="22">
         <v>11</v>
       </c>
-      <c r="S38" s="22">
+      <c r="U39" s="22">
         <v>14</v>
       </c>
-      <c r="T38" s="7"/>
-    </row>
-    <row r="39" spans="1:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
+      <c r="V39" s="7"/>
+    </row>
+    <row r="40" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R39" s="22">
+      <c r="B40" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T40" s="22">
         <v>11</v>
       </c>
-      <c r="S39" s="22">
+      <c r="U40" s="22">
         <v>14</v>
       </c>
-      <c r="T39" s="7"/>
-    </row>
-    <row r="40" spans="1:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
+      <c r="V40" s="7"/>
+    </row>
+    <row r="41" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R40" s="22">
-        <v>11</v>
-      </c>
-      <c r="S40" s="22">
-        <v>14</v>
-      </c>
-      <c r="T40" s="7"/>
-    </row>
-    <row r="41" spans="1:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
+      <c r="B41" s="26" t="s">
         <v>79</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>80</v>
       </c>
       <c r="C41" s="22">
         <v>400</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="3" t="s">
@@ -2877,37 +3037,85 @@
       <c r="Q41" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="R41" s="22">
+      <c r="R41" s="3"/>
+      <c r="S41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T41" s="22">
         <v>11</v>
       </c>
-      <c r="S41" s="22">
+      <c r="U41" s="22">
         <v>14</v>
       </c>
-      <c r="T41" s="7"/>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="11"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="7"/>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V41" s="7"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="22">
+        <v>500</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R42" s="3">
+        <v>1</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="V42" s="7"/>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="26"/>
       <c r="C43" s="3"/>
@@ -2927,9 +3135,11 @@
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
-      <c r="T43" s="7"/>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="7"/>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="26"/>
       <c r="C44" s="3"/>
@@ -2949,9 +3159,11 @@
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
-      <c r="T44" s="7"/>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="7"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="26"/>
       <c r="C45" s="3"/>
@@ -2971,9 +3183,11 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
-      <c r="T45" s="7"/>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="7"/>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="26"/>
       <c r="C46" s="3"/>
@@ -2993,9 +3207,11 @@
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
-      <c r="T46" s="7"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="7"/>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
       <c r="B47" s="26"/>
       <c r="C47" s="3"/>
@@ -3015,9 +3231,11 @@
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
-      <c r="T47" s="7"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="7"/>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
       <c r="B48" s="26"/>
       <c r="C48" s="3"/>
@@ -3037,9 +3255,11 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
-      <c r="T48" s="7"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="7"/>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="B49" s="26"/>
       <c r="C49" s="3"/>
@@ -3059,9 +3279,11 @@
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
-      <c r="T49" s="7"/>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="7"/>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="B50" s="26"/>
       <c r="C50" s="3"/>
@@ -3081,9 +3303,11 @@
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
-      <c r="T50" s="7"/>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="7"/>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
       <c r="B51" s="26"/>
       <c r="C51" s="3"/>
@@ -3103,9 +3327,11 @@
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
-      <c r="T51" s="7"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="7"/>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
       <c r="B52" s="26"/>
       <c r="C52" s="3"/>
@@ -3125,9 +3351,11 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
-      <c r="T52" s="7"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="7"/>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="26"/>
       <c r="C53" s="3"/>
@@ -3147,9 +3375,11 @@
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
-      <c r="T53" s="7"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="7"/>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="26"/>
       <c r="C54" s="3"/>
@@ -3169,9 +3399,11 @@
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
-      <c r="T54" s="7"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="7"/>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
       <c r="B55" s="26"/>
       <c r="C55" s="3"/>
@@ -3191,9 +3423,11 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-      <c r="T55" s="7"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="7"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="26"/>
       <c r="C56" s="3"/>
@@ -3213,9 +3447,11 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-      <c r="T56" s="7"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="7"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
       <c r="B57" s="26"/>
       <c r="C57" s="3"/>
@@ -3235,9 +3471,11 @@
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
-      <c r="T57" s="7"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="7"/>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="26"/>
       <c r="C58" s="3"/>
@@ -3257,9 +3495,11 @@
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
-      <c r="T58" s="7"/>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="7"/>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="26"/>
       <c r="C59" s="3"/>
@@ -3279,9 +3519,11 @@
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
-      <c r="T59" s="7"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="7"/>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="26"/>
       <c r="C60" s="3"/>
@@ -3301,9 +3543,11 @@
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
-      <c r="T60" s="7"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="7"/>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="26"/>
       <c r="C61" s="3"/>
@@ -3323,9 +3567,11 @@
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
-      <c r="T61" s="7"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="26"/>
       <c r="C62" s="3"/>
@@ -3345,9 +3591,11 @@
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
-      <c r="T62" s="7"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="7"/>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="26"/>
       <c r="C63" s="3"/>
@@ -3367,9 +3615,11 @@
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
-      <c r="T63" s="7"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="7"/>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
       <c r="B64" s="26"/>
       <c r="C64" s="3"/>
@@ -3389,9 +3639,11 @@
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
-      <c r="T64" s="7"/>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="7"/>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
       <c r="B65" s="26"/>
       <c r="C65" s="3"/>
@@ -3411,9 +3663,11 @@
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
-      <c r="T65" s="7"/>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="7"/>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
       <c r="B66" s="26"/>
       <c r="C66" s="3"/>
@@ -3433,9 +3687,11 @@
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
-      <c r="T66" s="7"/>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="7"/>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
       <c r="B67" s="26"/>
       <c r="C67" s="3"/>
@@ -3455,9 +3711,11 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-      <c r="T67" s="7"/>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="7"/>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
       <c r="B68" s="26"/>
       <c r="C68" s="3"/>
@@ -3477,9 +3735,11 @@
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
-      <c r="T68" s="7"/>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="7"/>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
       <c r="B69" s="26"/>
       <c r="C69" s="3"/>
@@ -3499,9 +3759,11 @@
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
-      <c r="T69" s="7"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="7"/>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
       <c r="B70" s="26"/>
       <c r="C70" s="3"/>
@@ -3521,9 +3783,11 @@
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
-      <c r="T70" s="7"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="7"/>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
       <c r="B71" s="26"/>
       <c r="C71" s="3"/>
@@ -3543,9 +3807,11 @@
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
-      <c r="T71" s="7"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71" s="7"/>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="11"/>
       <c r="B72" s="26"/>
       <c r="C72" s="3"/>
@@ -3565,9 +3831,11 @@
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
-      <c r="T72" s="7"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="7"/>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="11"/>
       <c r="B73" s="26"/>
       <c r="C73" s="3"/>
@@ -3587,9 +3855,11 @@
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
-      <c r="T73" s="7"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="7"/>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="11"/>
       <c r="B74" s="26"/>
       <c r="C74" s="3"/>
@@ -3609,9 +3879,11 @@
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
-      <c r="T74" s="7"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="7"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="11"/>
       <c r="B75" s="26"/>
       <c r="C75" s="3"/>
@@ -3631,9 +3903,11 @@
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
-      <c r="T75" s="7"/>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="7"/>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="11"/>
       <c r="B76" s="26"/>
       <c r="C76" s="3"/>
@@ -3653,9 +3927,11 @@
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
-      <c r="T76" s="7"/>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="7"/>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="11"/>
       <c r="B77" s="26"/>
       <c r="C77" s="3"/>
@@ -3675,9 +3951,11 @@
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
-      <c r="T77" s="7"/>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77" s="7"/>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
       <c r="B78" s="26"/>
       <c r="C78" s="3"/>
@@ -3697,9 +3975,11 @@
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
-      <c r="T78" s="7"/>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="7"/>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="11"/>
       <c r="B79" s="26"/>
       <c r="C79" s="3"/>
@@ -3719,9 +3999,11 @@
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
-      <c r="T79" s="7"/>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79" s="7"/>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="11"/>
       <c r="B80" s="26"/>
       <c r="C80" s="3"/>
@@ -3741,9 +4023,11 @@
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
-      <c r="T80" s="7"/>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="7"/>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="11"/>
       <c r="B81" s="26"/>
       <c r="C81" s="3"/>
@@ -3763,9 +4047,11 @@
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
-      <c r="T81" s="7"/>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T81" s="3"/>
+      <c r="U81" s="3"/>
+      <c r="V81" s="7"/>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="11"/>
       <c r="B82" s="26"/>
       <c r="C82" s="3"/>
@@ -3785,9 +4071,11 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-      <c r="T82" s="7"/>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="7"/>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="11"/>
       <c r="B83" s="26"/>
       <c r="C83" s="3"/>
@@ -3807,9 +4095,11 @@
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
-      <c r="T83" s="7"/>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83" s="7"/>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="11"/>
       <c r="B84" s="26"/>
       <c r="C84" s="3"/>
@@ -3829,9 +4119,11 @@
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
-      <c r="T84" s="7"/>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="7"/>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" s="11"/>
       <c r="B85" s="26"/>
       <c r="C85" s="3"/>
@@ -3851,9 +4143,11 @@
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
-      <c r="T85" s="7"/>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85" s="7"/>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" s="11"/>
       <c r="B86" s="26"/>
       <c r="C86" s="3"/>
@@ -3873,9 +4167,11 @@
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
-      <c r="T86" s="7"/>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="7"/>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" s="11"/>
       <c r="B87" s="26"/>
       <c r="C87" s="3"/>
@@ -3895,9 +4191,11 @@
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
-      <c r="T87" s="7"/>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87" s="7"/>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" s="11"/>
       <c r="B88" s="26"/>
       <c r="C88" s="3"/>
@@ -3917,9 +4215,11 @@
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
-      <c r="T88" s="7"/>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="7"/>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" s="11"/>
       <c r="B89" s="26"/>
       <c r="C89" s="3"/>
@@ -3939,9 +4239,11 @@
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
-      <c r="T89" s="7"/>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T89" s="3"/>
+      <c r="U89" s="3"/>
+      <c r="V89" s="7"/>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="11"/>
       <c r="B90" s="26"/>
       <c r="C90" s="3"/>
@@ -3961,9 +4263,11 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-      <c r="T90" s="7"/>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="7"/>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" s="11"/>
       <c r="B91" s="26"/>
       <c r="C91" s="3"/>
@@ -3983,9 +4287,11 @@
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
-      <c r="T91" s="7"/>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T91" s="3"/>
+      <c r="U91" s="3"/>
+      <c r="V91" s="7"/>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" s="11"/>
       <c r="B92" s="26"/>
       <c r="C92" s="3"/>
@@ -4005,9 +4311,11 @@
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
-      <c r="T92" s="7"/>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="7"/>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" s="11"/>
       <c r="B93" s="26"/>
       <c r="C93" s="3"/>
@@ -4027,9 +4335,11 @@
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
-      <c r="T93" s="7"/>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T93" s="3"/>
+      <c r="U93" s="3"/>
+      <c r="V93" s="7"/>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" s="11"/>
       <c r="B94" s="26"/>
       <c r="C94" s="3"/>
@@ -4049,9 +4359,11 @@
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
-      <c r="T94" s="7"/>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="7"/>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" s="11"/>
       <c r="B95" s="26"/>
       <c r="C95" s="3"/>
@@ -4071,9 +4383,11 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-      <c r="T95" s="7"/>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+      <c r="V95" s="7"/>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" s="11"/>
       <c r="B96" s="26"/>
       <c r="C96" s="3"/>
@@ -4093,9 +4407,11 @@
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
-      <c r="T96" s="7"/>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="7"/>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" s="11"/>
       <c r="B97" s="26"/>
       <c r="C97" s="3"/>
@@ -4115,9 +4431,11 @@
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
-      <c r="T97" s="7"/>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T97" s="3"/>
+      <c r="U97" s="3"/>
+      <c r="V97" s="7"/>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" s="11"/>
       <c r="B98" s="26"/>
       <c r="C98" s="3"/>
@@ -4137,9 +4455,11 @@
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
-      <c r="T98" s="7"/>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="7"/>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="11"/>
       <c r="B99" s="26"/>
       <c r="C99" s="3"/>
@@ -4159,9 +4479,11 @@
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
-      <c r="T99" s="7"/>
-    </row>
-    <row r="100" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T99" s="3"/>
+      <c r="U99" s="3"/>
+      <c r="V99" s="7"/>
+    </row>
+    <row r="100" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="12"/>
       <c r="B100" s="29"/>
       <c r="C100" s="8"/>
@@ -4181,27 +4503,29 @@
       <c r="Q100" s="8"/>
       <c r="R100" s="8"/>
       <c r="S100" s="8"/>
-      <c r="T100" s="9"/>
+      <c r="T100" s="8"/>
+      <c r="U100" s="8"/>
+      <c r="V100" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="I8:Q8"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="E3:H3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:B10"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="H8:P8"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/01.Documentation/Control de versiones de Sistema.xlsx
+++ b/01.Documentation/Control de versiones de Sistema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Team Dropbox\JRODRIGUEZ\Repositorios\01.Rover\01.Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB364415-99B6-497E-A661-4474EDC44A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C2FD14-9605-4BB2-BCFD-7092E6DDD925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24CF4CE9-DAD2-45B7-A0D0-75488DFF3356}"/>
   </bookViews>
   <sheets>
     <sheet name="ROVER" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="86">
   <si>
     <t>Cambios</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>X</t>
-  </si>
-  <si>
-    <t>RCA/Universal</t>
   </si>
   <si>
     <t>Version
@@ -285,6 +282,24 @@
   <si>
     <t>HotFix Eliminacion Pull UP SWD en DCDC y 
 Fix R22 CPU no en BOM</t>
+  </si>
+  <si>
+    <t>5.0.0.0</t>
+  </si>
+  <si>
+    <t>RCA</t>
+  </si>
+  <si>
+    <t>Universal</t>
+  </si>
+  <si>
+    <t>Vantablack</t>
+  </si>
+  <si>
+    <t>Creacion del modelo Vantablack</t>
+  </si>
+  <si>
+    <t>VantaMachine</t>
   </si>
 </sst>
 </file>
@@ -442,7 +457,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -560,17 +575,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -578,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -640,9 +644,6 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -652,37 +653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -697,6 +668,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -706,8 +710,17 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1023,98 +1036,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BF0786-E6C7-4307-9339-45491EF3032D}">
-  <dimension ref="A1:S100"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="44.85546875" style="39" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="2" customWidth="1"/>
-    <col min="4" max="6" width="12.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="44.85546875" style="28" customWidth="1"/>
+    <col min="3" max="5" width="17.5703125" style="2" customWidth="1"/>
+    <col min="6" max="8" width="12.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:22" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="30" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" spans="1:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="32" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="24"/>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>24</v>
+      <c r="B6" s="33"/>
+    </row>
+    <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>23</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>0</v>
@@ -1125,162 +1149,190 @@
       <c r="D8" s="34"/>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="33" t="s">
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
+      <c r="T8" s="45"/>
+      <c r="U8" s="45"/>
+      <c r="V8" s="43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="38"/>
       <c r="B9" s="41"/>
       <c r="C9" s="16" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D9" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="G9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="H9" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="I9" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="J9" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="K9" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="L9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="M9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="O9" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="P9" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="Q9" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="P9" s="18" t="s">
+      <c r="R9" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="S9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="18" t="s">
+      <c r="T9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="R9" s="18" t="s">
+      <c r="U9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="S9" s="29"/>
-    </row>
-    <row r="10" spans="1:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
+      <c r="V9" s="44"/>
+    </row>
+    <row r="10" spans="1:22" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="39"/>
       <c r="B10" s="42"/>
       <c r="C10" s="4">
-        <f>MAX(C11:C37)</f>
+        <f>MAX(C11:C100)</f>
+        <v>400</v>
+      </c>
+      <c r="D10" s="4">
+        <f>MAX(D11:D100)</f>
+        <v>500</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" ref="E10:I10" si="0">MAX(E11:E100)</f>
         <v>125</v>
       </c>
-      <c r="D10" s="4">
-        <f t="shared" ref="D10:E10" si="0">MAX(D11:D37)</f>
+      <c r="F10" s="4">
+        <f t="shared" si="0"/>
         <v>313</v>
       </c>
-      <c r="E10" s="4">
+      <c r="G10" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="4">
-        <f>MAX(F11:F37)</f>
+      <c r="H10" s="4">
+        <f t="shared" si="0"/>
         <v>205</v>
       </c>
-      <c r="G10" s="5">
-        <f>MAX(G11:G100)</f>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="H10" s="5">
-        <f t="shared" ref="H10:O10" si="1">MAX(H11:H100)</f>
+      <c r="J10" s="5">
+        <f t="shared" ref="J10" si="1">MAX(J11:J100)</f>
         <v>6</v>
       </c>
-      <c r="I10" s="5">
-        <f t="shared" si="1"/>
+      <c r="K10" s="5">
+        <f t="shared" ref="K10" si="2">MAX(K11:K100)</f>
         <v>3</v>
       </c>
-      <c r="J10" s="5">
-        <f t="shared" si="1"/>
+      <c r="L10" s="5">
+        <f t="shared" ref="L10:M10" si="3">MAX(L11:L100)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="22">
-        <f t="shared" si="1"/>
+      <c r="M10" s="5">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="L10" s="5">
-        <f t="shared" si="1"/>
+      <c r="N10" s="5">
+        <f t="shared" ref="N10" si="4">MAX(N11:N100)</f>
         <v>1</v>
       </c>
-      <c r="M10" s="5">
-        <f t="shared" si="1"/>
+      <c r="O10" s="5">
+        <f t="shared" ref="O10" si="5">MAX(O11:O100)</f>
         <v>3</v>
       </c>
-      <c r="N10" s="5">
-        <f t="shared" si="1"/>
+      <c r="P10" s="5">
+        <f t="shared" ref="P10" si="6">MAX(P11:P100)</f>
         <v>7</v>
       </c>
-      <c r="O10" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q10" s="5">
+        <f t="shared" ref="Q10:R10" si="7">MAX(Q11:Q100)</f>
         <v>1</v>
       </c>
-      <c r="P10" s="6">
-        <f>MAX(P11:P100)</f>
+      <c r="R10" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S10" s="6">
+        <f>MAX(S11:S100)</f>
         <v>5</v>
       </c>
-      <c r="Q10" s="6">
-        <f t="shared" ref="Q10:R10" si="2">MAX(Q11:Q100)</f>
+      <c r="T10" s="6">
+        <f t="shared" ref="T10:U10" si="8">MAX(T11:T100)</f>
         <v>11</v>
       </c>
-      <c r="R10" s="6">
-        <f t="shared" si="2"/>
+      <c r="U10" s="6">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="S10" s="15"/>
-    </row>
-    <row r="11" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V10" s="15"/>
+    </row>
+    <row r="11" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -1292,22 +1344,29 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
-      <c r="S11" s="7"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="7"/>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1319,22 +1378,29 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
-      <c r="S12" s="7"/>
-    </row>
-    <row r="13" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="7"/>
+    </row>
+    <row r="13" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1346,124 +1412,141 @@
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="7"/>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="7"/>
+    </row>
+    <row r="14" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13">
         <v>121</v>
       </c>
-      <c r="D14" s="13">
+      <c r="F14" s="13">
         <v>121</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1">
         <v>5</v>
       </c>
-      <c r="H14" s="1">
+      <c r="J14" s="1">
         <v>5</v>
       </c>
-      <c r="I14" s="1">
+      <c r="K14" s="1">
         <v>2</v>
       </c>
-      <c r="J14" s="1">
+      <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="1">
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1">
         <v>5</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="T14" s="1">
         <v>9</v>
       </c>
-      <c r="R14" s="1">
+      <c r="U14" s="1">
         <v>10</v>
       </c>
-      <c r="S14" s="7"/>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V14" s="7"/>
+    </row>
+    <row r="15" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="13">
+      <c r="H15" s="13">
         <v>201</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S15" s="7"/>
-    </row>
-    <row r="16" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" s="7"/>
+    </row>
+    <row r="16" spans="1:22" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1473,44 +1556,51 @@
       <c r="J16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-      <c r="P16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S16" s="7"/>
-    </row>
-    <row r="17" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V16" s="7"/>
+    </row>
+    <row r="17" spans="1:22" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1520,44 +1610,51 @@
       <c r="J17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S17" s="7"/>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V17" s="7"/>
+    </row>
+    <row r="18" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="13">
         <v>122</v>
       </c>
-      <c r="D18" s="13">
+      <c r="F18" s="13">
         <v>122</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1567,27 +1664,34 @@
       <c r="J18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-      <c r="P18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S18" s="7"/>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18" s="7"/>
+    </row>
+    <row r="19" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1597,61 +1701,68 @@
         <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="13">
+      <c r="H19" s="13">
         <v>202</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
-      <c r="P19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S19" s="7"/>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V19" s="7"/>
+    </row>
+    <row r="20" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="13">
+        <v>34</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="13">
         <v>123</v>
       </c>
-      <c r="D20" s="13">
+      <c r="F20" s="13">
         <v>123</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
       </c>
@@ -1661,28 +1772,35 @@
       <c r="J20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="P20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S20" s="7"/>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V20" s="7"/>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="37" t="s">
-        <v>43</v>
+        <v>35</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>42</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>13</v>
@@ -1691,62 +1809,69 @@
         <v>13</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="13">
+      <c r="H21" s="13">
         <v>203</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-      <c r="P21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S21" s="7"/>
-    </row>
-    <row r="22" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V21" s="7"/>
+    </row>
+    <row r="22" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="14">
         <v>310</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -1755,75 +1880,89 @@
       <c r="J22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-      <c r="P22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S22" s="7"/>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="7"/>
+    </row>
+    <row r="23" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="13">
+      <c r="B23" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13">
         <v>123</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="13">
+      <c r="H23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="13">
         <v>6</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="J23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-      <c r="P23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R23" s="13">
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U23" s="13">
         <v>11</v>
       </c>
-      <c r="S23" s="7"/>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V23" s="7"/>
+    </row>
+    <row r="24" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="37" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>49</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>13</v>
@@ -1832,108 +1971,122 @@
         <v>13</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="13">
+      <c r="H24" s="13">
         <v>203</v>
       </c>
-      <c r="G24" s="13">
+      <c r="I24" s="13">
         <v>6</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="J24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
-      <c r="P24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S24" s="7"/>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V24" s="7"/>
+    </row>
+    <row r="25" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="14">
+        <v>52</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="14">
         <v>310</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="13">
+      <c r="H25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="13">
         <v>6</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="J25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
-      <c r="P25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S25" s="7"/>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V25" s="7"/>
+    </row>
+    <row r="26" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="13">
+      <c r="B26" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13">
         <v>124</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
       </c>
@@ -1943,28 +2096,35 @@
       <c r="J26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
-      <c r="P26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S26" s="7"/>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V26" s="7"/>
+    </row>
+    <row r="27" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="37" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>53</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>13</v>
@@ -1973,62 +2133,69 @@
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="13">
+      <c r="H27" s="13">
         <v>204</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-      <c r="P27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S27" s="7"/>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V27" s="7"/>
+    </row>
+    <row r="28" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="14">
+        <v>55</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="14">
         <v>311</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2037,45 +2204,52 @@
       <c r="J28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
-      <c r="P28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S28" s="7"/>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V28" s="7"/>
+    </row>
+    <row r="29" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="B29" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="14">
         <v>312</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2084,58 +2258,65 @@
       <c r="J29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-      <c r="P29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S29" s="7"/>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V29" s="7"/>
+    </row>
+    <row r="30" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="14">
+        <v>61</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="14">
         <v>125</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" s="14">
+      <c r="H30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="14">
         <v>6</v>
       </c>
-      <c r="I30" s="14">
+      <c r="K30" s="14">
         <v>3</v>
       </c>
-      <c r="J30" s="14">
+      <c r="L30" s="14">
         <v>1</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>22</v>
@@ -2146,53 +2327,60 @@
       <c r="O30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q30" s="3">
+      <c r="P30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R30" s="3"/>
+      <c r="S30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T30" s="3">
         <v>10</v>
       </c>
-      <c r="R30" s="3">
+      <c r="U30" s="3">
         <v>12</v>
       </c>
-      <c r="S30" s="7"/>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V30" s="7"/>
+    </row>
+    <row r="31" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F31" s="14">
+      <c r="H31" s="14">
         <v>205</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="14">
+      <c r="I31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="14">
         <v>6</v>
       </c>
-      <c r="I31" s="14">
+      <c r="K31" s="14">
         <v>3</v>
       </c>
-      <c r="J31" s="14">
+      <c r="L31" s="14">
         <v>1</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>22</v>
@@ -2203,53 +2391,60 @@
       <c r="O31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q31" s="3">
+      <c r="P31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R31" s="3"/>
+      <c r="S31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T31" s="3">
         <v>10</v>
       </c>
-      <c r="R31" s="3">
+      <c r="U31" s="3">
         <v>12</v>
       </c>
-      <c r="S31" s="7"/>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V31" s="7"/>
+    </row>
+    <row r="32" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="14">
+      <c r="C32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="14">
         <v>313</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="14">
+      <c r="H32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="14">
         <v>6</v>
       </c>
-      <c r="I32" s="14">
+      <c r="K32" s="14">
         <v>3</v>
       </c>
-      <c r="J32" s="14">
+      <c r="L32" s="14">
         <v>1</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>22</v>
@@ -2260,554 +2455,669 @@
       <c r="O32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R32" s="3"/>
+      <c r="S32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T32" s="3">
         <v>10</v>
       </c>
-      <c r="R32" s="3">
+      <c r="U32" s="3">
         <v>12</v>
       </c>
-      <c r="S32" s="7"/>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="V32" s="7"/>
+    </row>
+    <row r="33" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="14">
+      <c r="C33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="14">
         <v>125</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="14">
+      <c r="H33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="14">
         <v>6</v>
       </c>
-      <c r="I33" s="14">
+      <c r="K33" s="14">
         <v>3</v>
-      </c>
-      <c r="J33" s="14">
-        <v>1</v>
-      </c>
-      <c r="K33" s="14">
-        <v>2</v>
       </c>
       <c r="L33" s="14">
         <v>1</v>
       </c>
       <c r="M33" s="14">
+        <v>2</v>
+      </c>
+      <c r="N33" s="14">
+        <v>1</v>
+      </c>
+      <c r="O33" s="14">
         <v>3</v>
       </c>
-      <c r="N33" s="14">
+      <c r="P33" s="14">
         <v>7</v>
       </c>
-      <c r="O33" s="14">
+      <c r="Q33" s="14">
         <v>1</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="14"/>
+      <c r="S33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T33" s="3">
         <v>10</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>12</v>
       </c>
-      <c r="S33" s="7"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="V33" s="7"/>
+    </row>
+    <row r="34" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="22">
+        <v>8</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U34" s="3">
+        <v>13</v>
+      </c>
+      <c r="V34" s="7"/>
+    </row>
+    <row r="35" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="37" t="s">
+      <c r="B35" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="22">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U35" s="3">
+        <v>13</v>
+      </c>
+      <c r="V35" s="7"/>
+    </row>
+    <row r="36" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="22">
+        <v>8</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U36" s="3">
+        <v>13</v>
+      </c>
+      <c r="V36" s="7"/>
+    </row>
+    <row r="37" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="22">
+        <v>8</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U37" s="3">
+        <v>13</v>
+      </c>
+      <c r="V37" s="7"/>
+    </row>
+    <row r="38" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="23">
-        <v>8</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R34" s="3">
-        <v>13</v>
-      </c>
-      <c r="S34" s="7"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="23">
-        <v>8</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R35" s="3">
-        <v>13</v>
-      </c>
-      <c r="S35" s="7"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="23">
-        <v>8</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R36" s="3">
-        <v>13</v>
-      </c>
-      <c r="S36" s="7"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="23">
-        <v>8</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R37" s="3">
-        <v>13</v>
-      </c>
-      <c r="S37" s="7"/>
-    </row>
-    <row r="38" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
+      <c r="B38" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T38" s="22">
+        <v>11</v>
+      </c>
+      <c r="U38" s="22">
+        <v>14</v>
+      </c>
+      <c r="V38" s="7"/>
+    </row>
+    <row r="39" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="37" t="s">
+      <c r="B39" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T39" s="22">
+        <v>11</v>
+      </c>
+      <c r="U39" s="22">
+        <v>14</v>
+      </c>
+      <c r="V39" s="7"/>
+    </row>
+    <row r="40" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T40" s="22">
+        <v>11</v>
+      </c>
+      <c r="U40" s="22">
+        <v>14</v>
+      </c>
+      <c r="V40" s="7"/>
+    </row>
+    <row r="41" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="22">
+        <v>400</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T41" s="22">
+        <v>11</v>
+      </c>
+      <c r="U41" s="22">
+        <v>14</v>
+      </c>
+      <c r="V41" s="7"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q38" s="23">
-        <v>11</v>
-      </c>
-      <c r="R38" s="23">
-        <v>14</v>
-      </c>
-      <c r="S38" s="7"/>
-    </row>
-    <row r="39" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q39" s="23">
-        <v>11</v>
-      </c>
-      <c r="R39" s="23">
-        <v>14</v>
-      </c>
-      <c r="S39" s="7"/>
-    </row>
-    <row r="40" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q40" s="23">
-        <v>11</v>
-      </c>
-      <c r="R40" s="23">
-        <v>14</v>
-      </c>
-      <c r="S40" s="7"/>
-    </row>
-    <row r="41" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q41" s="23">
-        <v>11</v>
-      </c>
-      <c r="R41" s="23">
-        <v>14</v>
-      </c>
-      <c r="S41" s="7"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42" s="11"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="7"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B42" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="22">
+        <v>500</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R42" s="3">
+        <v>1</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="V42" s="7"/>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
-      <c r="B43" s="37"/>
+      <c r="B43" s="26"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -2824,11 +3134,14 @@
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
-      <c r="S43" s="7"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="7"/>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
-      <c r="B44" s="37"/>
+      <c r="B44" s="26"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -2845,11 +3158,14 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
-      <c r="S44" s="7"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="7"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
-      <c r="B45" s="37"/>
+      <c r="B45" s="26"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -2866,11 +3182,14 @@
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
-      <c r="S45" s="7"/>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="7"/>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
-      <c r="B46" s="37"/>
+      <c r="B46" s="26"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -2887,11 +3206,14 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
-      <c r="S46" s="7"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="7"/>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
-      <c r="B47" s="37"/>
+      <c r="B47" s="26"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -2908,11 +3230,14 @@
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
-      <c r="S47" s="7"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="7"/>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
-      <c r="B48" s="37"/>
+      <c r="B48" s="26"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2929,11 +3254,14 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
-      <c r="S48" s="7"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="7"/>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
-      <c r="B49" s="37"/>
+      <c r="B49" s="26"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -2950,11 +3278,14 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
-      <c r="S49" s="7"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="7"/>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
-      <c r="B50" s="37"/>
+      <c r="B50" s="26"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -2971,11 +3302,14 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
-      <c r="S50" s="7"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="7"/>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
-      <c r="B51" s="37"/>
+      <c r="B51" s="26"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -2992,11 +3326,14 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
-      <c r="S51" s="7"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="7"/>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
-      <c r="B52" s="37"/>
+      <c r="B52" s="26"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -3013,11 +3350,14 @@
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
-      <c r="S52" s="7"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="7"/>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
-      <c r="B53" s="37"/>
+      <c r="B53" s="26"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3034,11 +3374,14 @@
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
-      <c r="S53" s="7"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="7"/>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
-      <c r="B54" s="37"/>
+      <c r="B54" s="26"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -3055,11 +3398,14 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
-      <c r="S54" s="7"/>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="7"/>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
-      <c r="B55" s="37"/>
+      <c r="B55" s="26"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -3076,11 +3422,14 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-      <c r="S55" s="7"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="7"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
-      <c r="B56" s="37"/>
+      <c r="B56" s="26"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -3097,11 +3446,14 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-      <c r="S56" s="7"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="7"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
-      <c r="B57" s="37"/>
+      <c r="B57" s="26"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -3118,11 +3470,14 @@
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
-      <c r="S57" s="7"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="7"/>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
-      <c r="B58" s="37"/>
+      <c r="B58" s="26"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -3139,11 +3494,14 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
-      <c r="S58" s="7"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="7"/>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
-      <c r="B59" s="37"/>
+      <c r="B59" s="26"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -3160,11 +3518,14 @@
       <c r="P59" s="3"/>
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
-      <c r="S59" s="7"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="7"/>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
-      <c r="B60" s="37"/>
+      <c r="B60" s="26"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -3181,11 +3542,14 @@
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
-      <c r="S60" s="7"/>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="7"/>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
-      <c r="B61" s="37"/>
+      <c r="B61" s="26"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -3202,11 +3566,14 @@
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
-      <c r="S61" s="7"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
-      <c r="B62" s="37"/>
+      <c r="B62" s="26"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -3223,11 +3590,14 @@
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
-      <c r="S62" s="7"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="7"/>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
-      <c r="B63" s="37"/>
+      <c r="B63" s="26"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3244,11 +3614,14 @@
       <c r="P63" s="3"/>
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
-      <c r="S63" s="7"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="7"/>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
-      <c r="B64" s="37"/>
+      <c r="B64" s="26"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -3265,11 +3638,14 @@
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
-      <c r="S64" s="7"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="7"/>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
-      <c r="B65" s="37"/>
+      <c r="B65" s="26"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3286,11 +3662,14 @@
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
-      <c r="S65" s="7"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S65" s="3"/>
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="7"/>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="11"/>
-      <c r="B66" s="37"/>
+      <c r="B66" s="26"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3307,11 +3686,14 @@
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
-      <c r="S66" s="7"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="7"/>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
-      <c r="B67" s="37"/>
+      <c r="B67" s="26"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3328,11 +3710,14 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-      <c r="S67" s="7"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="7"/>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
-      <c r="B68" s="37"/>
+      <c r="B68" s="26"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3349,11 +3734,14 @@
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
-      <c r="S68" s="7"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="7"/>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
-      <c r="B69" s="37"/>
+      <c r="B69" s="26"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -3370,11 +3758,14 @@
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
-      <c r="S69" s="7"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S69" s="3"/>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="7"/>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
-      <c r="B70" s="37"/>
+      <c r="B70" s="26"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -3391,11 +3782,14 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
-      <c r="S70" s="7"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="7"/>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
-      <c r="B71" s="37"/>
+      <c r="B71" s="26"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -3412,11 +3806,14 @@
       <c r="P71" s="3"/>
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
-      <c r="S71" s="7"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S71" s="3"/>
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71" s="7"/>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="11"/>
-      <c r="B72" s="37"/>
+      <c r="B72" s="26"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -3433,11 +3830,14 @@
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
-      <c r="S72" s="7"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="7"/>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="11"/>
-      <c r="B73" s="37"/>
+      <c r="B73" s="26"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -3454,11 +3854,14 @@
       <c r="P73" s="3"/>
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
-      <c r="S73" s="7"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S73" s="3"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="7"/>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="11"/>
-      <c r="B74" s="37"/>
+      <c r="B74" s="26"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -3475,11 +3878,14 @@
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
-      <c r="S74" s="7"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="7"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="11"/>
-      <c r="B75" s="37"/>
+      <c r="B75" s="26"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -3496,11 +3902,14 @@
       <c r="P75" s="3"/>
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
-      <c r="S75" s="7"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S75" s="3"/>
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="7"/>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="11"/>
-      <c r="B76" s="37"/>
+      <c r="B76" s="26"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3517,11 +3926,14 @@
       <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
-      <c r="S76" s="7"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="7"/>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="11"/>
-      <c r="B77" s="37"/>
+      <c r="B77" s="26"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3538,11 +3950,14 @@
       <c r="P77" s="3"/>
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
-      <c r="S77" s="7"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S77" s="3"/>
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77" s="7"/>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
-      <c r="B78" s="37"/>
+      <c r="B78" s="26"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -3559,11 +3974,14 @@
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
-      <c r="S78" s="7"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S78" s="3"/>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="7"/>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="11"/>
-      <c r="B79" s="37"/>
+      <c r="B79" s="26"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -3580,11 +3998,14 @@
       <c r="P79" s="3"/>
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
-      <c r="S79" s="7"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S79" s="3"/>
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79" s="7"/>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="11"/>
-      <c r="B80" s="37"/>
+      <c r="B80" s="26"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -3601,11 +4022,14 @@
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
-      <c r="S80" s="7"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="7"/>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="11"/>
-      <c r="B81" s="37"/>
+      <c r="B81" s="26"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -3622,11 +4046,14 @@
       <c r="P81" s="3"/>
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
-      <c r="S81" s="7"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S81" s="3"/>
+      <c r="T81" s="3"/>
+      <c r="U81" s="3"/>
+      <c r="V81" s="7"/>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="11"/>
-      <c r="B82" s="37"/>
+      <c r="B82" s="26"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -3643,11 +4070,14 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-      <c r="S82" s="7"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="7"/>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="11"/>
-      <c r="B83" s="37"/>
+      <c r="B83" s="26"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -3664,11 +4094,14 @@
       <c r="P83" s="3"/>
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
-      <c r="S83" s="7"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S83" s="3"/>
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83" s="7"/>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="11"/>
-      <c r="B84" s="37"/>
+      <c r="B84" s="26"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -3685,11 +4118,14 @@
       <c r="P84" s="3"/>
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
-      <c r="S84" s="7"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="7"/>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" s="11"/>
-      <c r="B85" s="37"/>
+      <c r="B85" s="26"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -3706,11 +4142,14 @@
       <c r="P85" s="3"/>
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
-      <c r="S85" s="7"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S85" s="3"/>
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85" s="7"/>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" s="11"/>
-      <c r="B86" s="37"/>
+      <c r="B86" s="26"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -3727,11 +4166,14 @@
       <c r="P86" s="3"/>
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
-      <c r="S86" s="7"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="7"/>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" s="11"/>
-      <c r="B87" s="37"/>
+      <c r="B87" s="26"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -3748,11 +4190,14 @@
       <c r="P87" s="3"/>
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
-      <c r="S87" s="7"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S87" s="3"/>
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87" s="7"/>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" s="11"/>
-      <c r="B88" s="37"/>
+      <c r="B88" s="26"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -3769,11 +4214,14 @@
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
-      <c r="S88" s="7"/>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="7"/>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" s="11"/>
-      <c r="B89" s="37"/>
+      <c r="B89" s="26"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -3790,11 +4238,14 @@
       <c r="P89" s="3"/>
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
-      <c r="S89" s="7"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S89" s="3"/>
+      <c r="T89" s="3"/>
+      <c r="U89" s="3"/>
+      <c r="V89" s="7"/>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="11"/>
-      <c r="B90" s="37"/>
+      <c r="B90" s="26"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -3811,11 +4262,14 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-      <c r="S90" s="7"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="7"/>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" s="11"/>
-      <c r="B91" s="37"/>
+      <c r="B91" s="26"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -3832,11 +4286,14 @@
       <c r="P91" s="3"/>
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
-      <c r="S91" s="7"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S91" s="3"/>
+      <c r="T91" s="3"/>
+      <c r="U91" s="3"/>
+      <c r="V91" s="7"/>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" s="11"/>
-      <c r="B92" s="37"/>
+      <c r="B92" s="26"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -3853,11 +4310,14 @@
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
-      <c r="S92" s="7"/>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="7"/>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" s="11"/>
-      <c r="B93" s="37"/>
+      <c r="B93" s="26"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -3874,11 +4334,14 @@
       <c r="P93" s="3"/>
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
-      <c r="S93" s="7"/>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S93" s="3"/>
+      <c r="T93" s="3"/>
+      <c r="U93" s="3"/>
+      <c r="V93" s="7"/>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" s="11"/>
-      <c r="B94" s="37"/>
+      <c r="B94" s="26"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -3895,11 +4358,14 @@
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
-      <c r="S94" s="7"/>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="7"/>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" s="11"/>
-      <c r="B95" s="37"/>
+      <c r="B95" s="26"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -3916,11 +4382,14 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-      <c r="S95" s="7"/>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+      <c r="V95" s="7"/>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" s="11"/>
-      <c r="B96" s="37"/>
+      <c r="B96" s="26"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -3937,11 +4406,14 @@
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
-      <c r="S96" s="7"/>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S96" s="3"/>
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="7"/>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" s="11"/>
-      <c r="B97" s="37"/>
+      <c r="B97" s="26"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -3958,11 +4430,14 @@
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
-      <c r="S97" s="7"/>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S97" s="3"/>
+      <c r="T97" s="3"/>
+      <c r="U97" s="3"/>
+      <c r="V97" s="7"/>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" s="11"/>
-      <c r="B98" s="37"/>
+      <c r="B98" s="26"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -3979,11 +4454,14 @@
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
-      <c r="S98" s="7"/>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S98" s="3"/>
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="7"/>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="11"/>
-      <c r="B99" s="37"/>
+      <c r="B99" s="26"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -4000,11 +4478,14 @@
       <c r="P99" s="3"/>
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
-      <c r="S99" s="7"/>
-    </row>
-    <row r="100" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S99" s="3"/>
+      <c r="T99" s="3"/>
+      <c r="U99" s="3"/>
+      <c r="V99" s="7"/>
+    </row>
+    <row r="100" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="12"/>
-      <c r="B100" s="43"/>
+      <c r="B100" s="29"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
@@ -4021,27 +4502,30 @@
       <c r="P100" s="8"/>
       <c r="Q100" s="8"/>
       <c r="R100" s="8"/>
-      <c r="S100" s="9"/>
+      <c r="S100" s="8"/>
+      <c r="T100" s="8"/>
+      <c r="U100" s="8"/>
+      <c r="V100" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="I8:Q8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="E3:H3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:B10"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:O8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
